--- a/files/Templates/collected_data.xlsx
+++ b/files/Templates/collected_data.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marpo\Documents\Research\STICS\Code\mkSTICSfiles\files\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B2079A-76F3-4845-AD5F-CC3D716C6DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8435BD-6E33-4294-89A4-E4A9A779B45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="30936" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="management" sheetId="8" r:id="rId1"/>
     <sheet name="soils" sheetId="5" r:id="rId2"/>
     <sheet name="stations" sheetId="6" r:id="rId3"/>
     <sheet name="usms" sheetId="1" r:id="rId4"/>
-    <sheet name="options" sheetId="4" r:id="rId5"/>
+    <sheet name="observations" sheetId="9" r:id="rId5"/>
+    <sheet name="options" sheetId="4" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Fertilizer_Application">Table3[Fertilizer_Application]</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="169">
   <si>
     <t>usm_name</t>
   </si>
@@ -426,9 +427,6 @@
     <t>Irrigation</t>
   </si>
   <si>
-    <t>k</t>
-  </si>
-  <si>
     <t>SOM_1</t>
   </si>
   <si>
@@ -502,6 +500,63 @@
   </si>
   <si>
     <t>Nitrogen Units</t>
+  </si>
+  <si>
+    <t>horizon_5</t>
+  </si>
+  <si>
+    <t>thickness_5</t>
+  </si>
+  <si>
+    <t>%_sand_5</t>
+  </si>
+  <si>
+    <t>%_clay_5</t>
+  </si>
+  <si>
+    <t>BD_5</t>
+  </si>
+  <si>
+    <t>SOC_5</t>
+  </si>
+  <si>
+    <t>FC_5</t>
+  </si>
+  <si>
+    <t>FC_5_unit</t>
+  </si>
+  <si>
+    <t>WP_5</t>
+  </si>
+  <si>
+    <t>WP_5_unit</t>
+  </si>
+  <si>
+    <t>initial_NO3_5</t>
+  </si>
+  <si>
+    <t>initial_NO3_5_unit</t>
+  </si>
+  <si>
+    <t>initial_NH4_5</t>
+  </si>
+  <si>
+    <t>initial_NH4_5_unit</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>variable 2</t>
+  </si>
+  <si>
+    <t>variable 1</t>
+  </si>
+  <si>
+    <t>albedo</t>
   </si>
 </sst>
 </file>
@@ -546,7 +601,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,8 +728,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="gray0625">
+        <fgColor theme="0" tint="-0.24994659260841701"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="gray0625">
+        <fgColor theme="0" tint="-0.24994659260841701"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -788,11 +873,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -801,15 +917,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -823,6 +933,35 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -841,13 +980,19 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -856,278 +1001,15 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="55">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -1202,6 +1084,467 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="1"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1221,12 +1564,12 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCCFF"/>
       <color rgb="FFECF4FA"/>
       <color rgb="FFEFF6EA"/>
       <color rgb="FFFFFBEF"/>
@@ -1248,24 +1591,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AT3" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32">
-  <autoFilter ref="A2:AT3" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AT100" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7">
+  <autoFilter ref="A2:AT100" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
   <tableColumns count="46">
-    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{416116E5-319A-4096-B7E5-AF8ADEF0E80A}" name="tillage_date"/>
-    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{A768ED69-1CCB-4A41-99C1-D5042177408B}" name="planting_date"/>
     <tableColumn id="6" xr3:uid="{5517C570-4D1C-46EC-9FB0-4FEA929440E1}" name="planting_depth"/>
-    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{7DEB259C-DAE3-4A1E-B476-951FEF30ABD2}" name="emergence"/>
     <tableColumn id="9" xr3:uid="{8590CC43-CF1F-45A9-A612-CE3749B53C84}" name="flowering"/>
-    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="1"/>
     <tableColumn id="11" xr3:uid="{1651DE3B-149A-4121-AFB0-BA33E8308050}" name="application_date"/>
     <tableColumn id="12" xr3:uid="{358B23A5-F859-4B79-9182-F98F3D69F461}" name="kg_N_per_ha"/>
     <tableColumn id="13" xr3:uid="{FEB67719-45D9-4389-A438-548C552EBED6}" name="fert_type"/>
     <tableColumn id="14" xr3:uid="{B9B3005C-6E63-4AA3-BE8E-646D9659B76F}" name="fert_location"/>
-    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="26"/>
+    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{AA12C7D8-D645-4337-B05C-CB5F5C197AE4}" name="irrigation_date_1"/>
     <tableColumn id="17" xr3:uid="{017BC113-D478-4E04-AEE6-020CA6B48738}" name="amount_1"/>
     <tableColumn id="18" xr3:uid="{498ED556-89DC-49A5-A6C1-DF741DBED2EF}" name="irrigation_date_2"/>
@@ -1302,13 +1645,24 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{38082219-60DA-4A2D-BE84-54584CE20A1B}" name="Table9" displayName="Table9" ref="I1:I3" totalsRowShown="0">
+  <autoFilter ref="I1:I3" xr:uid="{38082219-60DA-4A2D-BE84-54584CE20A1B}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{79460CD6-4F26-4C6D-8875-F9DB638BEE07}" name="Nitrogen Units"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:BE3" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12">
-  <autoFilter ref="A2:BE3" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
-  <tableColumns count="57">
-    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:BS100" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52">
+  <autoFilter ref="A2:BS100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
+  <tableColumns count="71">
+    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="51"/>
     <tableColumn id="2" xr3:uid="{72D785FE-A1AF-4E08-AB14-39FAD15DB9BD}" name="thickness_1"/>
     <tableColumn id="3" xr3:uid="{1838D7E8-2B3C-471C-9A0B-D70D91F18417}" name="pH"/>
+    <tableColumn id="71" xr3:uid="{931F79EB-F524-439C-8A88-ED674075FA7F}" name="albedo"/>
     <tableColumn id="4" xr3:uid="{22C3A2D3-19B8-4556-9BAC-DEDF286C1C2C}" name="%_sand_1"/>
     <tableColumn id="5" xr3:uid="{1040C5A7-CB33-4419-8EA9-5541F66164AB}" name="%_clay_1"/>
     <tableColumn id="6" xr3:uid="{B2FB90E9-0C4B-4F1F-8CF8-A6B1B8736BCF}" name="BD_1"/>
@@ -1317,90 +1671,118 @@
     <tableColumn id="40" xr3:uid="{EC836542-6DD7-49C9-82D9-B724BCE18341}" name="SON_1"/>
     <tableColumn id="41" xr3:uid="{F7750E58-5B0E-4494-87AF-B025671824DE}" name="CN_ratio"/>
     <tableColumn id="8" xr3:uid="{0592115C-328E-42C4-B9CB-D43026D4FC27}" name="FC_1"/>
-    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit"/>
+    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="50"/>
     <tableColumn id="9" xr3:uid="{C1383A59-387E-4667-852A-B0CF467088F3}" name="WP_1"/>
-    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit"/>
+    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="49"/>
     <tableColumn id="10" xr3:uid="{34D0D911-5DB4-457F-88A7-76A42B57EE1A}" name="initial_NO3_1"/>
-    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units"/>
+    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="48"/>
     <tableColumn id="53" xr3:uid="{CEF78893-60AA-4A20-A771-E76562B8EBC1}" name="initial_NH4_1"/>
-    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="47"/>
     <tableColumn id="12" xr3:uid="{FD043EB5-2678-4920-8D76-EBE8316E27AA}" name="thickness_2"/>
     <tableColumn id="13" xr3:uid="{F124AE04-B447-4F21-A0E8-7B26199C0F49}" name="%_sand_2"/>
     <tableColumn id="14" xr3:uid="{F119498A-3A35-40E3-A753-7CF13D724118}" name="%_clay_2"/>
     <tableColumn id="15" xr3:uid="{AE51522F-6903-42D4-88CE-A95BCE8C77EF}" name="BD_2"/>
     <tableColumn id="16" xr3:uid="{12076489-6AD7-4297-A729-20EF93AEE58D}" name="SOC_2"/>
     <tableColumn id="17" xr3:uid="{D6D5EFD4-69CC-4AF2-8C6B-0B430468C4C2}" name="FC_2"/>
-    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit"/>
+    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="46"/>
     <tableColumn id="18" xr3:uid="{BBF6A61D-2092-4DF7-8C38-9024164291AE}" name="WP_2"/>
-    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit"/>
+    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="45"/>
     <tableColumn id="19" xr3:uid="{BB4B796C-CA3E-424C-87B0-4BF33581B61B}" name="initial_NO3_2"/>
-    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit"/>
+    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="44"/>
     <tableColumn id="55" xr3:uid="{333E59C3-3A13-4C92-9169-AC90D5E5D3EB}" name="initial_NH4_2"/>
-    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3"/>
+    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="43"/>
+    <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3" dataDxfId="42"/>
     <tableColumn id="22" xr3:uid="{6C917DE4-8D95-496E-A6F1-EAB7450774EE}" name="%_sand_3"/>
     <tableColumn id="23" xr3:uid="{90DE7FE2-3A23-4294-8BD0-2D321FF71179}" name="%_clay_3"/>
     <tableColumn id="24" xr3:uid="{C874CBBB-CB06-4239-AE9B-72564A3EDC14}" name="BD_3"/>
     <tableColumn id="25" xr3:uid="{49CED3FB-E83C-4973-A99D-DAC6B3AFC7B1}" name="SOC_3"/>
     <tableColumn id="26" xr3:uid="{63FB3901-EBED-4379-9E9C-83064A8ADD01}" name="FC_3"/>
-    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit"/>
+    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="41"/>
     <tableColumn id="27" xr3:uid="{6EEACF0E-3934-49DF-9991-42C2DB718BE0}" name="WP_3"/>
-    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit"/>
+    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="40"/>
     <tableColumn id="28" xr3:uid="{7AAE3F1E-C60E-4E11-A023-F09548D5AA39}" name="initial_NO3_3"/>
-    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit"/>
+    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="39"/>
     <tableColumn id="57" xr3:uid="{1D0A3587-38DB-4073-B5D4-36DA82425955}" name="initial_NH4_3"/>
-    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="7"/>
-    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4"/>
+    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="38"/>
+    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="37"/>
     <tableColumn id="31" xr3:uid="{4C1178FA-055B-4F19-A181-638D37A24EB6}" name="%_sand_4"/>
     <tableColumn id="32" xr3:uid="{7BBFA3FD-BBE5-4B68-A551-EFDEA7062540}" name="%_clay_4"/>
     <tableColumn id="33" xr3:uid="{D0607A27-FB9E-4DA9-A7F3-7A932B2608A4}" name="BD_4"/>
     <tableColumn id="34" xr3:uid="{BD46131F-AB56-411A-8742-B77FBBE1967B}" name="SOC_4"/>
     <tableColumn id="35" xr3:uid="{EC2EEDB8-3CC6-4DEE-9309-DBA3B11A2D16}" name="FC_4"/>
-    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="6"/>
-    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="5"/>
-    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="4"/>
-    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="3"/>
-    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="2"/>
-    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="1"/>
-    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="0"/>
+    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="36"/>
+    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="35"/>
+    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="34"/>
+    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="33"/>
+    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="32"/>
+    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="31"/>
+    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="30"/>
+    <tableColumn id="46" xr3:uid="{5545ADBB-3E57-4FCE-9979-330500D810A6}" name="thickness_5"/>
+    <tableColumn id="49" xr3:uid="{28F4610E-A232-42D7-866E-B72AB5FC38D8}" name="%_sand_5"/>
+    <tableColumn id="60" xr3:uid="{9557F7B0-0944-4CA4-8B86-630B4073480C}" name="%_clay_5"/>
+    <tableColumn id="61" xr3:uid="{6977D0A0-E571-46FB-8186-DF22D992C4B6}" name="BD_5"/>
+    <tableColumn id="62" xr3:uid="{762BF513-B3A9-4714-B788-A74D32CD414B}" name="SOC_5"/>
+    <tableColumn id="63" xr3:uid="{F840DA58-F957-445A-8704-4823DC13AEC7}" name="FC_5"/>
+    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="29"/>
+    <tableColumn id="65" xr3:uid="{73133DDD-77CC-4B8F-AF63-0B5537B95DE3}" name="WP_5"/>
+    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="28"/>
+    <tableColumn id="67" xr3:uid="{AF697735-FE14-47A1-8029-532D47D2E5C7}" name="initial_NO3_5"/>
+    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="27"/>
+    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="26"/>
+    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:D2" totalsRowShown="0" headerRowBorderDxfId="25" tableBorderDxfId="24">
-  <autoFilter ref="A1:D2" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:D109" totalsRowShown="0" headerRowBorderDxfId="24" tableBorderDxfId="23">
+  <autoFilter ref="A1:D109" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:J3" totalsRowShown="0" headerRowBorderDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A2:J3" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:J100" totalsRowShown="0" headerRowBorderDxfId="18" tableBorderDxfId="17">
+  <autoFilter ref="A2:J100" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{C58B90D4-B75A-409B-9D58-E09932ABF65C}" name="simulation_start"/>
-    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name"/>
+    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="14"/>
     <tableColumn id="5" xr3:uid="{C4CB74A7-2660-4D67-9D08-D7802D112D6D}" name="soil_profile_name"/>
     <tableColumn id="6" xr3:uid="{EE8564A9-D685-42B6-914D-B5F77F840B11}" name="weather_station_name"/>
-    <tableColumn id="7" xr3:uid="{DF70C6E4-2795-4D3D-B86B-8B48BE8FB3E1}" name="plant_file" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{B3D6750F-E334-4A3F-A048-BA40F1D2EC0C}" name="cultivar_code" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{DF70C6E4-2795-4D3D-B86B-8B48BE8FB3E1}" name="plant_file"/>
+    <tableColumn id="8" xr3:uid="{B3D6750F-E334-4A3F-A048-BA40F1D2EC0C}" name="cultivar_code" dataDxfId="13"/>
     <tableColumn id="9" xr3:uid="{BDB57316-D9C6-4EE3-821F-F5561E0078D9}" name="first_year"/>
-    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year"/>
+    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="11">
+  <autoFilter ref="A1:F30" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A5156817-2D3F-4E14-AC57-75BA66E12293}" name="year"/>
+    <tableColumn id="3" xr3:uid="{173E3383-07EB-425D-884F-01E4ECFF4626}" name="month"/>
+    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{B9B2B184-EF64-48EF-B50B-8E24249DFDCC}" name="variable 1"/>
+    <tableColumn id="7" xr3:uid="{ED0F5D28-DB43-4C9B-ADB2-1706AC6D61F9}" name="variable 2"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CDF66EE8-361B-4202-8A1F-0D5EDF285F75}" name="Table1" displayName="Table1" ref="A1:A5" totalsRowShown="0">
   <autoFilter ref="A1:A5" xr:uid="{CDF66EE8-361B-4202-8A1F-0D5EDF285F75}"/>
   <tableColumns count="1">
@@ -1410,7 +1792,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4A152238-69C8-4363-98E6-0F0F1C2B2617}" name="Table2" displayName="Table2" ref="C1:C9" totalsRowShown="0">
   <autoFilter ref="C1:C9" xr:uid="{4A152238-69C8-4363-98E6-0F0F1C2B2617}"/>
   <tableColumns count="1">
@@ -1420,7 +1802,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A574AAF-4FAA-4157-AC4A-8B9D21C891D1}" name="Table3" displayName="Table3" ref="E1:E3" totalsRowShown="0">
   <autoFilter ref="E1:E3" xr:uid="{6A574AAF-4FAA-4157-AC4A-8B9D21C891D1}"/>
   <tableColumns count="1">
@@ -1430,21 +1812,11 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8070D148-86D5-42F4-953C-3FD3B59B038F}" name="Table4" displayName="Table4" ref="G1:G3" totalsRowShown="0">
   <autoFilter ref="G1:G3" xr:uid="{8070D148-86D5-42F4-953C-3FD3B59B038F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{8C51BBDC-E41E-4966-B7A2-2ADDB3FCD779}" name="Soil Moisture Units"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{38082219-60DA-4A2D-BE84-54584CE20A1B}" name="Table9" displayName="Table9" ref="I1:I3" totalsRowShown="0">
-  <autoFilter ref="I1:I3" xr:uid="{38082219-60DA-4A2D-BE84-54584CE20A1B}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{79460CD6-4F26-4C6D-8875-F9DB638BEE07}" name="Nitrogen Units"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1716,24 +2088,24 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AT100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="19.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="6"/>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" style="6" customWidth="1"/>
     <col min="5" max="5" width="15.109375" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.109375" customWidth="1"/>
     <col min="9" max="9" width="11.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" style="6" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="14.109375" customWidth="1"/>
     <col min="13" max="13" width="10.6640625" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" style="7" customWidth="1"/>
+    <col min="15" max="15" width="15.44140625" style="6" customWidth="1"/>
     <col min="16" max="16" width="17.21875" customWidth="1"/>
     <col min="17" max="17" width="11.5546875" customWidth="1"/>
     <col min="18" max="18" width="17.21875" customWidth="1"/>
@@ -1768,81 +2140,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="51"/>
+      <c r="E1" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="29" t="s">
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="28" t="s">
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="30" t="s">
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="30"/>
-      <c r="AL1" s="30"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="30"/>
-      <c r="AO1" s="30"/>
-      <c r="AP1" s="30"/>
-      <c r="AQ1" s="30"/>
-      <c r="AR1" s="30"/>
-      <c r="AS1" s="30"/>
-      <c r="AT1" s="30"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="55"/>
+      <c r="AC1" s="55"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="55"/>
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="55"/>
+      <c r="AR1" s="55"/>
+      <c r="AS1" s="55"/>
+      <c r="AT1" s="55"/>
     </row>
     <row r="2" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="17" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="13" t="s">
         <v>56</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -1851,123 +2223,511 @@
       <c r="I2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="T2" s="15" t="s">
+      <c r="T2" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="X2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="Z2" s="15" t="s">
+      <c r="Z2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="AA2" s="15" t="s">
+      <c r="AA2" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AD2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AE2" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="AF2" s="15" t="s">
+      <c r="AF2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AG2" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AK2" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AL2" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="AM2" s="15" t="s">
+      <c r="AM2" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AN2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AO2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AP2" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AR2" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AS2" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="AT2" s="15" t="s">
+      <c r="AT2" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>125</v>
-      </c>
+      <c r="E3" s="67"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
       <c r="AT3"/>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+    </row>
+    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+    </row>
+    <row r="17" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+    </row>
+    <row r="18" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+    </row>
+    <row r="19" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+    </row>
+    <row r="20" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+    </row>
+    <row r="21" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+    </row>
+    <row r="22" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+    </row>
+    <row r="23" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+    </row>
+    <row r="24" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+    </row>
+    <row r="25" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+    </row>
+    <row r="26" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+    </row>
+    <row r="27" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+    </row>
+    <row r="28" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+    </row>
+    <row r="29" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+    </row>
+    <row r="30" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+    </row>
+    <row r="31" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+    </row>
+    <row r="32" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+    </row>
+    <row r="33" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+    </row>
+    <row r="34" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+    </row>
+    <row r="35" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+    </row>
+    <row r="36" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+    </row>
+    <row r="37" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+    </row>
+    <row r="38" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+    </row>
+    <row r="39" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+    </row>
+    <row r="40" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
+    </row>
+    <row r="41" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+    </row>
+    <row r="42" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+    </row>
+    <row r="43" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+    </row>
+    <row r="44" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+    </row>
+    <row r="45" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+    </row>
+    <row r="46" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+    </row>
+    <row r="47" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M47" s="38"/>
+      <c r="N47" s="38"/>
+    </row>
+    <row r="48" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M48" s="38"/>
+      <c r="N48" s="38"/>
+    </row>
+    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M49" s="38"/>
+      <c r="N49" s="38"/>
+    </row>
+    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M50" s="38"/>
+      <c r="N50" s="38"/>
+    </row>
+    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M51" s="38"/>
+      <c r="N51" s="38"/>
+    </row>
+    <row r="52" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M52" s="38"/>
+      <c r="N52" s="38"/>
+    </row>
+    <row r="53" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+    </row>
+    <row r="54" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+    </row>
+    <row r="55" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+    </row>
+    <row r="56" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M56" s="38"/>
+      <c r="N56" s="38"/>
+    </row>
+    <row r="57" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+    </row>
+    <row r="58" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M58" s="38"/>
+      <c r="N58" s="38"/>
+    </row>
+    <row r="59" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M59" s="38"/>
+      <c r="N59" s="38"/>
+    </row>
+    <row r="60" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M60" s="38"/>
+      <c r="N60" s="38"/>
+    </row>
+    <row r="61" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M61" s="38"/>
+      <c r="N61" s="38"/>
+    </row>
+    <row r="62" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M62" s="38"/>
+      <c r="N62" s="38"/>
+    </row>
+    <row r="63" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="38"/>
+      <c r="N63" s="38"/>
+    </row>
+    <row r="64" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M64" s="38"/>
+      <c r="N64" s="38"/>
+    </row>
+    <row r="65" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M65" s="38"/>
+      <c r="N65" s="38"/>
+    </row>
+    <row r="66" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M66" s="38"/>
+      <c r="N66" s="38"/>
+    </row>
+    <row r="67" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M67" s="38"/>
+      <c r="N67" s="38"/>
+    </row>
+    <row r="68" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M68" s="38"/>
+      <c r="N68" s="38"/>
+    </row>
+    <row r="69" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M69" s="38"/>
+      <c r="N69" s="38"/>
+    </row>
+    <row r="70" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M70" s="38"/>
+      <c r="N70" s="38"/>
+    </row>
+    <row r="71" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M71" s="38"/>
+      <c r="N71" s="38"/>
+    </row>
+    <row r="72" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M72" s="38"/>
+      <c r="N72" s="38"/>
+    </row>
+    <row r="73" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M73" s="38"/>
+      <c r="N73" s="38"/>
+    </row>
+    <row r="74" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M74" s="38"/>
+      <c r="N74" s="38"/>
+    </row>
+    <row r="75" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M75" s="38"/>
+      <c r="N75" s="38"/>
+    </row>
+    <row r="76" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M76" s="38"/>
+      <c r="N76" s="38"/>
+    </row>
+    <row r="77" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M77" s="38"/>
+      <c r="N77" s="38"/>
+    </row>
+    <row r="78" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M78" s="38"/>
+      <c r="N78" s="38"/>
+    </row>
+    <row r="79" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M79" s="38"/>
+      <c r="N79" s="38"/>
+    </row>
+    <row r="80" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M80" s="38"/>
+      <c r="N80" s="38"/>
+    </row>
+    <row r="81" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M81" s="38"/>
+      <c r="N81" s="38"/>
+    </row>
+    <row r="82" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M82" s="38"/>
+      <c r="N82" s="38"/>
+    </row>
+    <row r="83" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M83" s="38"/>
+      <c r="N83" s="38"/>
+    </row>
+    <row r="84" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M84" s="38"/>
+      <c r="N84" s="38"/>
+    </row>
+    <row r="85" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M85" s="38"/>
+      <c r="N85" s="38"/>
+    </row>
+    <row r="86" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M86" s="38"/>
+      <c r="N86" s="38"/>
+    </row>
+    <row r="87" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M87" s="38"/>
+      <c r="N87" s="38"/>
+    </row>
+    <row r="88" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M88" s="38"/>
+      <c r="N88" s="38"/>
+    </row>
+    <row r="89" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M89" s="38"/>
+      <c r="N89" s="38"/>
+    </row>
+    <row r="90" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M90" s="38"/>
+      <c r="N90" s="38"/>
+    </row>
+    <row r="91" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M91" s="38"/>
+      <c r="N91" s="38"/>
+    </row>
+    <row r="92" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M92" s="38"/>
+      <c r="N92" s="38"/>
+    </row>
+    <row r="93" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M93" s="38"/>
+      <c r="N93" s="38"/>
+    </row>
+    <row r="94" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M94" s="38"/>
+      <c r="N94" s="38"/>
+    </row>
+    <row r="95" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M95" s="38"/>
+      <c r="N95" s="38"/>
+    </row>
+    <row r="96" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M96" s="38"/>
+      <c r="N96" s="38"/>
+    </row>
+    <row r="97" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M97" s="38"/>
+      <c r="N97" s="38"/>
+    </row>
+    <row r="98" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M98" s="38"/>
+      <c r="N98" s="38"/>
+    </row>
+    <row r="99" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M99" s="38"/>
+      <c r="N99" s="38"/>
+    </row>
+    <row r="100" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M100" s="38"/>
+      <c r="N100" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1985,17 +2745,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select" xr:uid="{EFEC405D-8F3B-4A88-81A8-C05C829F992E}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="fertilizer" prompt="select type" xr:uid="{B70B515A-9E4D-43A4-A403-3B52F4B6E7A5}">
           <x14:formula1>
             <xm:f>options!$C$2:$C$9</xm:f>
           </x14:formula1>
-          <xm:sqref>M3</xm:sqref>
+          <xm:sqref>M3:M100</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select" xr:uid="{78A622A6-5FD1-4C73-8594-7ECF9C674B63}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="fertilizer location" prompt="Indicate if fertlizer broadcasted aboveground or incorperated below ground. If belowground indicate at what depth (cm) in column to the right." xr:uid="{4A205F64-CD6A-4C87-A5B8-AE72051B4B8A}">
           <x14:formula1>
             <xm:f>options!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>N3</xm:sqref>
+          <xm:sqref>N3:N100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2008,290 +2768,3179 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:BE3"/>
+  <dimension ref="A1:BS100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="21.77734375" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="15" max="17" width="17.77734375" customWidth="1"/>
-    <col min="18" max="18" width="14" style="7" customWidth="1"/>
+    <col min="18" max="18" width="14" style="6" customWidth="1"/>
     <col min="19" max="19" width="12.6640625" customWidth="1"/>
     <col min="20" max="20" width="11.33203125" customWidth="1"/>
     <col min="21" max="21" width="10.6640625" customWidth="1"/>
     <col min="28" max="30" width="14.109375" customWidth="1"/>
-    <col min="31" max="31" width="16" style="7" customWidth="1"/>
+    <col min="31" max="31" width="16" style="6" customWidth="1"/>
     <col min="32" max="32" width="12.6640625" customWidth="1"/>
     <col min="33" max="33" width="11.33203125" customWidth="1"/>
     <col min="34" max="34" width="10.6640625" customWidth="1"/>
     <col min="41" max="43" width="14.109375" customWidth="1"/>
-    <col min="44" max="44" width="14" style="7" customWidth="1"/>
+    <col min="44" max="44" width="14" style="6" customWidth="1"/>
     <col min="45" max="45" width="12.6640625" customWidth="1"/>
     <col min="46" max="46" width="11.33203125" customWidth="1"/>
     <col min="47" max="47" width="10.6640625" customWidth="1"/>
     <col min="55" max="56" width="14.109375" customWidth="1"/>
-    <col min="57" max="57" width="14" style="5" customWidth="1"/>
+    <col min="57" max="57" width="14" style="6" customWidth="1"/>
     <col min="58" max="58" width="12.44140625" customWidth="1"/>
+    <col min="70" max="70" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="B1" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="27" t="s">
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="26" t="s">
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="52"/>
+      <c r="AC1" s="52"/>
+      <c r="AD1" s="52"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
-      <c r="AM1" s="26"/>
-      <c r="AN1" s="26"/>
-      <c r="AO1" s="26"/>
-      <c r="AP1" s="26"/>
-      <c r="AQ1" s="26"/>
-      <c r="AR1" s="26"/>
-      <c r="AS1" s="30" t="s">
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="AT1" s="30"/>
-      <c r="AU1" s="30"/>
-      <c r="AV1" s="30"/>
-      <c r="AW1" s="30"/>
-      <c r="AX1" s="30"/>
-      <c r="AY1" s="30"/>
-      <c r="AZ1" s="30"/>
-      <c r="BA1" s="30"/>
-      <c r="BB1" s="30"/>
-      <c r="BC1" s="30"/>
-      <c r="BD1" s="30"/>
-      <c r="BE1" s="32"/>
-    </row>
-    <row r="2" spans="1:57" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="AT1" s="55"/>
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="55"/>
+      <c r="BB1" s="55"/>
+      <c r="BC1" s="55"/>
+      <c r="BD1" s="55"/>
+      <c r="BE1" s="57"/>
+      <c r="BF1" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="BG1" s="58"/>
+      <c r="BH1" s="58"/>
+      <c r="BI1" s="58"/>
+      <c r="BJ1" s="58"/>
+      <c r="BK1" s="58"/>
+      <c r="BL1" s="58"/>
+      <c r="BM1" s="58"/>
+      <c r="BN1" s="58"/>
+      <c r="BO1" s="58"/>
+      <c r="BP1" s="58"/>
+      <c r="BQ1" s="58"/>
+      <c r="BR1" s="59"/>
+    </row>
+    <row r="2" spans="1:71" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="F2" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="G2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="H2" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="42" t="s">
+      <c r="K2" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="J2" s="42" t="s">
+      <c r="L2" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="37" t="s">
+      <c r="N2" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="M2" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="37" t="s">
+      <c r="P2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="T2" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y2" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="O2" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q2" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="38" t="s">
+      <c r="AA2" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD2" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="S2" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="V2" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y2" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z2" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA2" s="39" t="s">
+      <c r="AE2" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF2" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG2" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH2" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI2" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ2" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK2" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AL2" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM2" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="AB2" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC2" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD2" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE2" s="40" t="s">
+      <c r="AN2" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO2" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="AP2" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ2" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="AF2" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG2" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH2" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI2" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ2" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL2" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM2" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN2" s="49" t="s">
+      <c r="AR2" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS2" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT2" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU2" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV2" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="AW2" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="AX2" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY2" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ2" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="AO2" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP2" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="AQ2" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="AR2" s="50" t="s">
+      <c r="BA2" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="BB2" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="BC2" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD2" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="AS2" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="AT2" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU2" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="AV2" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="AW2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="AX2" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY2" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="AZ2" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA2" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="BB2" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="BC2" s="52" t="s">
+      <c r="BE2" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="BF2" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="BD2" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="BE2" s="52" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="BG2" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="BH2" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="BI2" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ2" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="BK2" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="BL2" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="BM2" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="BN2" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="BO2" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="BP2" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="BQ2" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="BR2" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS2" s="48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="Q3" s="38"/>
       <c r="R3"/>
+      <c r="S3" s="42"/>
+      <c r="Z3" s="38"/>
+      <c r="AB3" s="38"/>
+      <c r="AD3" s="38"/>
       <c r="AE3"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="43"/>
+      <c r="AM3" s="38"/>
+      <c r="AO3" s="38"/>
+      <c r="AQ3" s="38"/>
       <c r="AR3"/>
-      <c r="AY3" s="53"/>
-      <c r="AZ3" s="53"/>
-      <c r="BA3" s="53"/>
-      <c r="BB3" s="53"/>
-      <c r="BC3" s="53"/>
-      <c r="BD3" s="53"/>
-      <c r="BE3" s="53"/>
+      <c r="AS3" s="38"/>
+      <c r="AT3" s="43"/>
+      <c r="AZ3" s="38"/>
+      <c r="BB3" s="38"/>
+      <c r="BD3" s="38"/>
+      <c r="BE3"/>
+      <c r="BF3" s="41"/>
+      <c r="BM3" s="38"/>
+      <c r="BO3" s="38"/>
+      <c r="BQ3" s="38"/>
+      <c r="BR3"/>
+      <c r="BS3" s="38"/>
+    </row>
+    <row r="4" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4"/>
+      <c r="S4" s="41"/>
+      <c r="Z4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="21"/>
+      <c r="AM4" s="38"/>
+      <c r="AO4" s="38"/>
+      <c r="AQ4" s="38"/>
+      <c r="AR4"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="21"/>
+      <c r="AZ4" s="38"/>
+      <c r="BB4" s="38"/>
+      <c r="BD4" s="38"/>
+      <c r="BE4"/>
+      <c r="BF4" s="41"/>
+      <c r="BM4" s="38"/>
+      <c r="BO4" s="38"/>
+      <c r="BQ4" s="38"/>
+      <c r="BR4"/>
+      <c r="BS4" s="38"/>
+    </row>
+    <row r="5" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5"/>
+      <c r="S5" s="41"/>
+      <c r="Z5" s="38"/>
+      <c r="AB5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="21"/>
+      <c r="AM5" s="38"/>
+      <c r="AO5" s="38"/>
+      <c r="AQ5" s="38"/>
+      <c r="AR5"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="21"/>
+      <c r="AZ5" s="38"/>
+      <c r="BB5" s="38"/>
+      <c r="BD5" s="38"/>
+      <c r="BE5"/>
+      <c r="BF5" s="41"/>
+      <c r="BM5" s="38"/>
+      <c r="BO5" s="38"/>
+      <c r="BQ5" s="38"/>
+      <c r="BR5"/>
+      <c r="BS5" s="38"/>
+    </row>
+    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6"/>
+      <c r="S6" s="41"/>
+      <c r="Z6" s="38"/>
+      <c r="AB6" s="38"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="21"/>
+      <c r="AM6" s="38"/>
+      <c r="AO6" s="38"/>
+      <c r="AQ6" s="38"/>
+      <c r="AR6"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="21"/>
+      <c r="AZ6" s="38"/>
+      <c r="BB6" s="38"/>
+      <c r="BD6" s="38"/>
+      <c r="BE6"/>
+      <c r="BF6" s="41"/>
+      <c r="BM6" s="38"/>
+      <c r="BO6" s="38"/>
+      <c r="BQ6" s="38"/>
+      <c r="BR6"/>
+      <c r="BS6" s="38"/>
+    </row>
+    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7"/>
+      <c r="S7" s="41"/>
+      <c r="Z7" s="38"/>
+      <c r="AB7" s="38"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="21"/>
+      <c r="AM7" s="38"/>
+      <c r="AO7" s="38"/>
+      <c r="AQ7" s="38"/>
+      <c r="AR7"/>
+      <c r="AS7" s="41"/>
+      <c r="AT7" s="21"/>
+      <c r="AZ7" s="38"/>
+      <c r="BB7" s="38"/>
+      <c r="BD7" s="38"/>
+      <c r="BE7"/>
+      <c r="BF7" s="41"/>
+      <c r="BM7" s="38"/>
+      <c r="BO7" s="38"/>
+      <c r="BQ7" s="38"/>
+      <c r="BR7"/>
+      <c r="BS7" s="38"/>
+    </row>
+    <row r="8" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8"/>
+      <c r="S8" s="41"/>
+      <c r="Z8" s="38"/>
+      <c r="AB8" s="38"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8"/>
+      <c r="AF8" s="41"/>
+      <c r="AG8" s="21"/>
+      <c r="AM8" s="38"/>
+      <c r="AO8" s="38"/>
+      <c r="AQ8" s="38"/>
+      <c r="AR8"/>
+      <c r="AS8" s="41"/>
+      <c r="AT8" s="21"/>
+      <c r="AZ8" s="38"/>
+      <c r="BB8" s="38"/>
+      <c r="BD8" s="38"/>
+      <c r="BE8"/>
+      <c r="BF8" s="41"/>
+      <c r="BM8" s="38"/>
+      <c r="BO8" s="38"/>
+      <c r="BQ8" s="38"/>
+      <c r="BR8"/>
+      <c r="BS8" s="38"/>
+    </row>
+    <row r="9" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9"/>
+      <c r="S9" s="41"/>
+      <c r="Z9" s="38"/>
+      <c r="AB9" s="38"/>
+      <c r="AD9" s="38"/>
+      <c r="AE9"/>
+      <c r="AF9" s="41"/>
+      <c r="AG9" s="21"/>
+      <c r="AM9" s="38"/>
+      <c r="AO9" s="38"/>
+      <c r="AQ9" s="38"/>
+      <c r="AR9"/>
+      <c r="AS9" s="41"/>
+      <c r="AT9" s="21"/>
+      <c r="AZ9" s="38"/>
+      <c r="BB9" s="38"/>
+      <c r="BD9" s="38"/>
+      <c r="BE9"/>
+      <c r="BF9" s="41"/>
+      <c r="BM9" s="38"/>
+      <c r="BO9" s="38"/>
+      <c r="BQ9" s="38"/>
+      <c r="BR9"/>
+      <c r="BS9" s="38"/>
+    </row>
+    <row r="10" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10"/>
+      <c r="S10" s="41"/>
+      <c r="Z10" s="38"/>
+      <c r="AB10" s="38"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10"/>
+      <c r="AF10" s="41"/>
+      <c r="AG10" s="21"/>
+      <c r="AM10" s="38"/>
+      <c r="AO10" s="38"/>
+      <c r="AQ10" s="38"/>
+      <c r="AR10"/>
+      <c r="AS10" s="41"/>
+      <c r="AT10" s="21"/>
+      <c r="AZ10" s="38"/>
+      <c r="BB10" s="38"/>
+      <c r="BD10" s="38"/>
+      <c r="BE10"/>
+      <c r="BF10" s="41"/>
+      <c r="BM10" s="38"/>
+      <c r="BO10" s="38"/>
+      <c r="BQ10" s="38"/>
+      <c r="BR10"/>
+      <c r="BS10" s="38"/>
+    </row>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11"/>
+      <c r="S11" s="41"/>
+      <c r="Z11" s="38"/>
+      <c r="AB11" s="38"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="21"/>
+      <c r="AM11" s="38"/>
+      <c r="AO11" s="38"/>
+      <c r="AQ11" s="38"/>
+      <c r="AR11"/>
+      <c r="AS11" s="41"/>
+      <c r="AT11" s="21"/>
+      <c r="AZ11" s="38"/>
+      <c r="BB11" s="38"/>
+      <c r="BD11" s="38"/>
+      <c r="BE11"/>
+      <c r="BF11" s="41"/>
+      <c r="BM11" s="38"/>
+      <c r="BO11" s="38"/>
+      <c r="BQ11" s="38"/>
+      <c r="BR11"/>
+      <c r="BS11" s="38"/>
+    </row>
+    <row r="12" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12"/>
+      <c r="S12" s="41"/>
+      <c r="Z12" s="38"/>
+      <c r="AB12" s="38"/>
+      <c r="AD12" s="38"/>
+      <c r="AE12"/>
+      <c r="AF12" s="41"/>
+      <c r="AG12" s="21"/>
+      <c r="AM12" s="38"/>
+      <c r="AO12" s="38"/>
+      <c r="AQ12" s="38"/>
+      <c r="AR12"/>
+      <c r="AS12" s="41"/>
+      <c r="AT12" s="21"/>
+      <c r="AZ12" s="38"/>
+      <c r="BB12" s="38"/>
+      <c r="BD12" s="38"/>
+      <c r="BE12"/>
+      <c r="BF12" s="41"/>
+      <c r="BM12" s="38"/>
+      <c r="BO12" s="38"/>
+      <c r="BQ12" s="38"/>
+      <c r="BR12"/>
+      <c r="BS12" s="38"/>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13"/>
+      <c r="S13" s="41"/>
+      <c r="Z13" s="38"/>
+      <c r="AB13" s="38"/>
+      <c r="AD13" s="38"/>
+      <c r="AE13"/>
+      <c r="AF13" s="41"/>
+      <c r="AG13" s="21"/>
+      <c r="AM13" s="38"/>
+      <c r="AO13" s="38"/>
+      <c r="AQ13" s="38"/>
+      <c r="AR13"/>
+      <c r="AS13" s="41"/>
+      <c r="AT13" s="21"/>
+      <c r="AZ13" s="38"/>
+      <c r="BB13" s="38"/>
+      <c r="BD13" s="38"/>
+      <c r="BE13"/>
+      <c r="BF13" s="41"/>
+      <c r="BM13" s="38"/>
+      <c r="BO13" s="38"/>
+      <c r="BQ13" s="38"/>
+      <c r="BR13"/>
+      <c r="BS13" s="38"/>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14"/>
+      <c r="S14" s="41"/>
+      <c r="Z14" s="38"/>
+      <c r="AB14" s="38"/>
+      <c r="AD14" s="38"/>
+      <c r="AE14"/>
+      <c r="AF14" s="41"/>
+      <c r="AG14" s="21"/>
+      <c r="AM14" s="38"/>
+      <c r="AO14" s="38"/>
+      <c r="AQ14" s="38"/>
+      <c r="AR14"/>
+      <c r="AS14" s="41"/>
+      <c r="AT14" s="21"/>
+      <c r="AZ14" s="38"/>
+      <c r="BB14" s="38"/>
+      <c r="BD14" s="38"/>
+      <c r="BE14"/>
+      <c r="BF14" s="41"/>
+      <c r="BM14" s="38"/>
+      <c r="BO14" s="38"/>
+      <c r="BQ14" s="38"/>
+      <c r="BR14"/>
+      <c r="BS14" s="38"/>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15"/>
+      <c r="S15" s="41"/>
+      <c r="Z15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="21"/>
+      <c r="AM15" s="38"/>
+      <c r="AO15" s="38"/>
+      <c r="AQ15" s="38"/>
+      <c r="AR15"/>
+      <c r="AS15" s="41"/>
+      <c r="AT15" s="21"/>
+      <c r="AZ15" s="38"/>
+      <c r="BB15" s="38"/>
+      <c r="BD15" s="38"/>
+      <c r="BE15"/>
+      <c r="BF15" s="41"/>
+      <c r="BM15" s="38"/>
+      <c r="BO15" s="38"/>
+      <c r="BQ15" s="38"/>
+      <c r="BR15"/>
+      <c r="BS15" s="38"/>
+    </row>
+    <row r="16" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="M16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16"/>
+      <c r="S16" s="41"/>
+      <c r="Z16" s="38"/>
+      <c r="AB16" s="38"/>
+      <c r="AD16" s="38"/>
+      <c r="AE16"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="21"/>
+      <c r="AM16" s="38"/>
+      <c r="AO16" s="38"/>
+      <c r="AQ16" s="38"/>
+      <c r="AR16"/>
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="21"/>
+      <c r="AZ16" s="38"/>
+      <c r="BB16" s="38"/>
+      <c r="BD16" s="38"/>
+      <c r="BE16"/>
+      <c r="BF16" s="41"/>
+      <c r="BM16" s="38"/>
+      <c r="BO16" s="38"/>
+      <c r="BQ16" s="38"/>
+      <c r="BR16"/>
+      <c r="BS16" s="38"/>
+    </row>
+    <row r="17" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17"/>
+      <c r="S17" s="41"/>
+      <c r="Z17" s="38"/>
+      <c r="AB17" s="38"/>
+      <c r="AD17" s="38"/>
+      <c r="AE17"/>
+      <c r="AF17" s="41"/>
+      <c r="AG17" s="21"/>
+      <c r="AM17" s="38"/>
+      <c r="AO17" s="38"/>
+      <c r="AQ17" s="38"/>
+      <c r="AR17"/>
+      <c r="AS17" s="41"/>
+      <c r="AT17" s="21"/>
+      <c r="AZ17" s="38"/>
+      <c r="BB17" s="38"/>
+      <c r="BD17" s="38"/>
+      <c r="BE17"/>
+      <c r="BF17" s="41"/>
+      <c r="BM17" s="38"/>
+      <c r="BO17" s="38"/>
+      <c r="BQ17" s="38"/>
+      <c r="BR17"/>
+      <c r="BS17" s="38"/>
+    </row>
+    <row r="18" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18"/>
+      <c r="S18" s="41"/>
+      <c r="Z18" s="38"/>
+      <c r="AB18" s="38"/>
+      <c r="AD18" s="38"/>
+      <c r="AE18"/>
+      <c r="AF18" s="41"/>
+      <c r="AG18" s="21"/>
+      <c r="AM18" s="38"/>
+      <c r="AO18" s="38"/>
+      <c r="AQ18" s="38"/>
+      <c r="AR18"/>
+      <c r="AS18" s="41"/>
+      <c r="AT18" s="21"/>
+      <c r="AZ18" s="38"/>
+      <c r="BB18" s="38"/>
+      <c r="BD18" s="38"/>
+      <c r="BE18"/>
+      <c r="BF18" s="41"/>
+      <c r="BM18" s="38"/>
+      <c r="BO18" s="38"/>
+      <c r="BQ18" s="38"/>
+      <c r="BR18"/>
+      <c r="BS18" s="38"/>
+    </row>
+    <row r="19" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19"/>
+      <c r="S19" s="41"/>
+      <c r="Z19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19"/>
+      <c r="AF19" s="41"/>
+      <c r="AG19" s="21"/>
+      <c r="AM19" s="38"/>
+      <c r="AO19" s="38"/>
+      <c r="AQ19" s="38"/>
+      <c r="AR19"/>
+      <c r="AS19" s="41"/>
+      <c r="AT19" s="21"/>
+      <c r="AZ19" s="38"/>
+      <c r="BB19" s="38"/>
+      <c r="BD19" s="38"/>
+      <c r="BE19"/>
+      <c r="BF19" s="41"/>
+      <c r="BM19" s="38"/>
+      <c r="BO19" s="38"/>
+      <c r="BQ19" s="38"/>
+      <c r="BR19"/>
+      <c r="BS19" s="38"/>
+    </row>
+    <row r="20" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20"/>
+      <c r="S20" s="41"/>
+      <c r="Z20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AD20" s="38"/>
+      <c r="AE20"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="21"/>
+      <c r="AM20" s="38"/>
+      <c r="AO20" s="38"/>
+      <c r="AQ20" s="38"/>
+      <c r="AR20"/>
+      <c r="AS20" s="41"/>
+      <c r="AT20" s="21"/>
+      <c r="AZ20" s="38"/>
+      <c r="BB20" s="38"/>
+      <c r="BD20" s="38"/>
+      <c r="BE20"/>
+      <c r="BF20" s="41"/>
+      <c r="BM20" s="38"/>
+      <c r="BO20" s="38"/>
+      <c r="BQ20" s="38"/>
+      <c r="BR20"/>
+      <c r="BS20" s="38"/>
+    </row>
+    <row r="21" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21"/>
+      <c r="S21" s="41"/>
+      <c r="Z21" s="38"/>
+      <c r="AB21" s="38"/>
+      <c r="AD21" s="38"/>
+      <c r="AE21"/>
+      <c r="AF21" s="41"/>
+      <c r="AG21" s="21"/>
+      <c r="AM21" s="38"/>
+      <c r="AO21" s="38"/>
+      <c r="AQ21" s="38"/>
+      <c r="AR21"/>
+      <c r="AS21" s="41"/>
+      <c r="AT21" s="21"/>
+      <c r="AZ21" s="38"/>
+      <c r="BB21" s="38"/>
+      <c r="BD21" s="38"/>
+      <c r="BE21"/>
+      <c r="BF21" s="41"/>
+      <c r="BM21" s="38"/>
+      <c r="BO21" s="38"/>
+      <c r="BQ21" s="38"/>
+      <c r="BR21"/>
+      <c r="BS21" s="38"/>
+    </row>
+    <row r="22" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22"/>
+      <c r="S22" s="41"/>
+      <c r="Z22" s="38"/>
+      <c r="AB22" s="38"/>
+      <c r="AD22" s="38"/>
+      <c r="AE22"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="21"/>
+      <c r="AM22" s="38"/>
+      <c r="AO22" s="38"/>
+      <c r="AQ22" s="38"/>
+      <c r="AR22"/>
+      <c r="AS22" s="41"/>
+      <c r="AT22" s="21"/>
+      <c r="AZ22" s="38"/>
+      <c r="BB22" s="38"/>
+      <c r="BD22" s="38"/>
+      <c r="BE22"/>
+      <c r="BF22" s="41"/>
+      <c r="BM22" s="38"/>
+      <c r="BO22" s="38"/>
+      <c r="BQ22" s="38"/>
+      <c r="BR22"/>
+      <c r="BS22" s="38"/>
+    </row>
+    <row r="23" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23"/>
+      <c r="S23" s="41"/>
+      <c r="Z23" s="38"/>
+      <c r="AB23" s="38"/>
+      <c r="AD23" s="38"/>
+      <c r="AE23"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="21"/>
+      <c r="AM23" s="38"/>
+      <c r="AO23" s="38"/>
+      <c r="AQ23" s="38"/>
+      <c r="AR23"/>
+      <c r="AS23" s="41"/>
+      <c r="AT23" s="21"/>
+      <c r="AZ23" s="38"/>
+      <c r="BB23" s="38"/>
+      <c r="BD23" s="38"/>
+      <c r="BE23"/>
+      <c r="BF23" s="41"/>
+      <c r="BM23" s="38"/>
+      <c r="BO23" s="38"/>
+      <c r="BQ23" s="38"/>
+      <c r="BR23"/>
+      <c r="BS23" s="38"/>
+    </row>
+    <row r="24" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24"/>
+      <c r="S24" s="41"/>
+      <c r="Z24" s="38"/>
+      <c r="AB24" s="38"/>
+      <c r="AD24" s="38"/>
+      <c r="AE24"/>
+      <c r="AF24" s="41"/>
+      <c r="AG24" s="21"/>
+      <c r="AM24" s="38"/>
+      <c r="AO24" s="38"/>
+      <c r="AQ24" s="38"/>
+      <c r="AR24"/>
+      <c r="AS24" s="41"/>
+      <c r="AT24" s="21"/>
+      <c r="AZ24" s="38"/>
+      <c r="BB24" s="38"/>
+      <c r="BD24" s="38"/>
+      <c r="BE24"/>
+      <c r="BF24" s="41"/>
+      <c r="BM24" s="38"/>
+      <c r="BO24" s="38"/>
+      <c r="BQ24" s="38"/>
+      <c r="BR24"/>
+      <c r="BS24" s="38"/>
+    </row>
+    <row r="25" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25"/>
+      <c r="S25" s="41"/>
+      <c r="Z25" s="38"/>
+      <c r="AB25" s="38"/>
+      <c r="AD25" s="38"/>
+      <c r="AE25"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="21"/>
+      <c r="AM25" s="38"/>
+      <c r="AO25" s="38"/>
+      <c r="AQ25" s="38"/>
+      <c r="AR25"/>
+      <c r="AS25" s="41"/>
+      <c r="AT25" s="21"/>
+      <c r="AZ25" s="38"/>
+      <c r="BB25" s="38"/>
+      <c r="BD25" s="38"/>
+      <c r="BE25"/>
+      <c r="BF25" s="41"/>
+      <c r="BM25" s="38"/>
+      <c r="BO25" s="38"/>
+      <c r="BQ25" s="38"/>
+      <c r="BR25"/>
+      <c r="BS25" s="38"/>
+    </row>
+    <row r="26" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26"/>
+      <c r="S26" s="41"/>
+      <c r="Z26" s="38"/>
+      <c r="AB26" s="38"/>
+      <c r="AD26" s="38"/>
+      <c r="AE26"/>
+      <c r="AF26" s="41"/>
+      <c r="AG26" s="21"/>
+      <c r="AM26" s="38"/>
+      <c r="AO26" s="38"/>
+      <c r="AQ26" s="38"/>
+      <c r="AR26"/>
+      <c r="AS26" s="41"/>
+      <c r="AT26" s="21"/>
+      <c r="AZ26" s="38"/>
+      <c r="BB26" s="38"/>
+      <c r="BD26" s="38"/>
+      <c r="BE26"/>
+      <c r="BF26" s="41"/>
+      <c r="BM26" s="38"/>
+      <c r="BO26" s="38"/>
+      <c r="BQ26" s="38"/>
+      <c r="BR26"/>
+      <c r="BS26" s="38"/>
+    </row>
+    <row r="27" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27"/>
+      <c r="S27" s="41"/>
+      <c r="Z27" s="38"/>
+      <c r="AB27" s="38"/>
+      <c r="AD27" s="38"/>
+      <c r="AE27"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="21"/>
+      <c r="AM27" s="38"/>
+      <c r="AO27" s="38"/>
+      <c r="AQ27" s="38"/>
+      <c r="AR27"/>
+      <c r="AS27" s="41"/>
+      <c r="AT27" s="21"/>
+      <c r="AZ27" s="38"/>
+      <c r="BB27" s="38"/>
+      <c r="BD27" s="38"/>
+      <c r="BE27"/>
+      <c r="BF27" s="41"/>
+      <c r="BM27" s="38"/>
+      <c r="BO27" s="38"/>
+      <c r="BQ27" s="38"/>
+      <c r="BR27"/>
+      <c r="BS27" s="38"/>
+    </row>
+    <row r="28" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28"/>
+      <c r="S28" s="41"/>
+      <c r="Z28" s="38"/>
+      <c r="AB28" s="38"/>
+      <c r="AD28" s="38"/>
+      <c r="AE28"/>
+      <c r="AF28" s="41"/>
+      <c r="AG28" s="21"/>
+      <c r="AM28" s="38"/>
+      <c r="AO28" s="38"/>
+      <c r="AQ28" s="38"/>
+      <c r="AR28"/>
+      <c r="AS28" s="41"/>
+      <c r="AT28" s="21"/>
+      <c r="AZ28" s="38"/>
+      <c r="BB28" s="38"/>
+      <c r="BD28" s="38"/>
+      <c r="BE28"/>
+      <c r="BF28" s="41"/>
+      <c r="BM28" s="38"/>
+      <c r="BO28" s="38"/>
+      <c r="BQ28" s="38"/>
+      <c r="BR28"/>
+      <c r="BS28" s="38"/>
+    </row>
+    <row r="29" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29"/>
+      <c r="S29" s="41"/>
+      <c r="Z29" s="38"/>
+      <c r="AB29" s="38"/>
+      <c r="AD29" s="38"/>
+      <c r="AE29"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="21"/>
+      <c r="AM29" s="38"/>
+      <c r="AO29" s="38"/>
+      <c r="AQ29" s="38"/>
+      <c r="AR29"/>
+      <c r="AS29" s="41"/>
+      <c r="AT29" s="21"/>
+      <c r="AZ29" s="38"/>
+      <c r="BB29" s="38"/>
+      <c r="BD29" s="38"/>
+      <c r="BE29"/>
+      <c r="BF29" s="41"/>
+      <c r="BM29" s="38"/>
+      <c r="BO29" s="38"/>
+      <c r="BQ29" s="38"/>
+      <c r="BR29"/>
+      <c r="BS29" s="38"/>
+    </row>
+    <row r="30" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30"/>
+      <c r="S30" s="41"/>
+      <c r="Z30" s="38"/>
+      <c r="AB30" s="38"/>
+      <c r="AD30" s="38"/>
+      <c r="AE30"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="21"/>
+      <c r="AM30" s="38"/>
+      <c r="AO30" s="38"/>
+      <c r="AQ30" s="38"/>
+      <c r="AR30"/>
+      <c r="AS30" s="41"/>
+      <c r="AT30" s="21"/>
+      <c r="AZ30" s="38"/>
+      <c r="BB30" s="38"/>
+      <c r="BD30" s="38"/>
+      <c r="BE30"/>
+      <c r="BF30" s="41"/>
+      <c r="BM30" s="38"/>
+      <c r="BO30" s="38"/>
+      <c r="BQ30" s="38"/>
+      <c r="BR30"/>
+      <c r="BS30" s="38"/>
+    </row>
+    <row r="31" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31"/>
+      <c r="S31" s="41"/>
+      <c r="Z31" s="38"/>
+      <c r="AB31" s="38"/>
+      <c r="AD31" s="38"/>
+      <c r="AE31"/>
+      <c r="AF31" s="41"/>
+      <c r="AG31" s="21"/>
+      <c r="AM31" s="38"/>
+      <c r="AO31" s="38"/>
+      <c r="AQ31" s="38"/>
+      <c r="AR31"/>
+      <c r="AS31" s="41"/>
+      <c r="AT31" s="21"/>
+      <c r="AZ31" s="38"/>
+      <c r="BB31" s="38"/>
+      <c r="BD31" s="38"/>
+      <c r="BE31"/>
+      <c r="BF31" s="41"/>
+      <c r="BM31" s="38"/>
+      <c r="BO31" s="38"/>
+      <c r="BQ31" s="38"/>
+      <c r="BR31"/>
+      <c r="BS31" s="38"/>
+    </row>
+    <row r="32" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32"/>
+      <c r="S32" s="41"/>
+      <c r="Z32" s="38"/>
+      <c r="AB32" s="38"/>
+      <c r="AD32" s="38"/>
+      <c r="AE32"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="21"/>
+      <c r="AM32" s="38"/>
+      <c r="AO32" s="38"/>
+      <c r="AQ32" s="38"/>
+      <c r="AR32"/>
+      <c r="AS32" s="41"/>
+      <c r="AT32" s="21"/>
+      <c r="AZ32" s="38"/>
+      <c r="BB32" s="38"/>
+      <c r="BD32" s="38"/>
+      <c r="BE32"/>
+      <c r="BF32" s="41"/>
+      <c r="BM32" s="38"/>
+      <c r="BO32" s="38"/>
+      <c r="BQ32" s="38"/>
+      <c r="BR32"/>
+      <c r="BS32" s="38"/>
+    </row>
+    <row r="33" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33"/>
+      <c r="S33" s="41"/>
+      <c r="Z33" s="38"/>
+      <c r="AB33" s="38"/>
+      <c r="AD33" s="38"/>
+      <c r="AE33"/>
+      <c r="AF33" s="41"/>
+      <c r="AG33" s="21"/>
+      <c r="AM33" s="38"/>
+      <c r="AO33" s="38"/>
+      <c r="AQ33" s="38"/>
+      <c r="AR33"/>
+      <c r="AS33" s="41"/>
+      <c r="AT33" s="21"/>
+      <c r="AZ33" s="38"/>
+      <c r="BB33" s="38"/>
+      <c r="BD33" s="38"/>
+      <c r="BE33"/>
+      <c r="BF33" s="41"/>
+      <c r="BM33" s="38"/>
+      <c r="BO33" s="38"/>
+      <c r="BQ33" s="38"/>
+      <c r="BR33"/>
+      <c r="BS33" s="38"/>
+    </row>
+    <row r="34" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34"/>
+      <c r="S34" s="41"/>
+      <c r="Z34" s="38"/>
+      <c r="AB34" s="38"/>
+      <c r="AD34" s="38"/>
+      <c r="AE34"/>
+      <c r="AF34" s="41"/>
+      <c r="AG34" s="21"/>
+      <c r="AM34" s="38"/>
+      <c r="AO34" s="38"/>
+      <c r="AQ34" s="38"/>
+      <c r="AR34"/>
+      <c r="AS34" s="41"/>
+      <c r="AT34" s="21"/>
+      <c r="AZ34" s="38"/>
+      <c r="BB34" s="38"/>
+      <c r="BD34" s="38"/>
+      <c r="BE34"/>
+      <c r="BF34" s="41"/>
+      <c r="BM34" s="38"/>
+      <c r="BO34" s="38"/>
+      <c r="BQ34" s="38"/>
+      <c r="BR34"/>
+      <c r="BS34" s="38"/>
+    </row>
+    <row r="35" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35"/>
+      <c r="S35" s="41"/>
+      <c r="Z35" s="38"/>
+      <c r="AB35" s="38"/>
+      <c r="AD35" s="38"/>
+      <c r="AE35"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="21"/>
+      <c r="AM35" s="38"/>
+      <c r="AO35" s="38"/>
+      <c r="AQ35" s="38"/>
+      <c r="AR35"/>
+      <c r="AS35" s="41"/>
+      <c r="AT35" s="21"/>
+      <c r="AZ35" s="38"/>
+      <c r="BB35" s="38"/>
+      <c r="BD35" s="38"/>
+      <c r="BE35"/>
+      <c r="BF35" s="41"/>
+      <c r="BM35" s="38"/>
+      <c r="BO35" s="38"/>
+      <c r="BQ35" s="38"/>
+      <c r="BR35"/>
+      <c r="BS35" s="38"/>
+    </row>
+    <row r="36" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36"/>
+      <c r="S36" s="41"/>
+      <c r="Z36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36"/>
+      <c r="AF36" s="41"/>
+      <c r="AG36" s="21"/>
+      <c r="AM36" s="38"/>
+      <c r="AO36" s="38"/>
+      <c r="AQ36" s="38"/>
+      <c r="AR36"/>
+      <c r="AS36" s="41"/>
+      <c r="AT36" s="21"/>
+      <c r="AZ36" s="38"/>
+      <c r="BB36" s="38"/>
+      <c r="BD36" s="38"/>
+      <c r="BE36"/>
+      <c r="BF36" s="41"/>
+      <c r="BM36" s="38"/>
+      <c r="BO36" s="38"/>
+      <c r="BQ36" s="38"/>
+      <c r="BR36"/>
+      <c r="BS36" s="38"/>
+    </row>
+    <row r="37" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37"/>
+      <c r="S37" s="41"/>
+      <c r="Z37" s="38"/>
+      <c r="AB37" s="38"/>
+      <c r="AD37" s="38"/>
+      <c r="AE37"/>
+      <c r="AF37" s="41"/>
+      <c r="AG37" s="21"/>
+      <c r="AM37" s="38"/>
+      <c r="AO37" s="38"/>
+      <c r="AQ37" s="38"/>
+      <c r="AR37"/>
+      <c r="AS37" s="41"/>
+      <c r="AT37" s="21"/>
+      <c r="AZ37" s="38"/>
+      <c r="BB37" s="38"/>
+      <c r="BD37" s="38"/>
+      <c r="BE37"/>
+      <c r="BF37" s="41"/>
+      <c r="BM37" s="38"/>
+      <c r="BO37" s="38"/>
+      <c r="BQ37" s="38"/>
+      <c r="BR37"/>
+      <c r="BS37" s="38"/>
+    </row>
+    <row r="38" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38"/>
+      <c r="S38" s="41"/>
+      <c r="Z38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38"/>
+      <c r="AF38" s="41"/>
+      <c r="AG38" s="21"/>
+      <c r="AM38" s="38"/>
+      <c r="AO38" s="38"/>
+      <c r="AQ38" s="38"/>
+      <c r="AR38"/>
+      <c r="AS38" s="41"/>
+      <c r="AT38" s="21"/>
+      <c r="AZ38" s="38"/>
+      <c r="BB38" s="38"/>
+      <c r="BD38" s="38"/>
+      <c r="BE38"/>
+      <c r="BF38" s="41"/>
+      <c r="BM38" s="38"/>
+      <c r="BO38" s="38"/>
+      <c r="BQ38" s="38"/>
+      <c r="BR38"/>
+      <c r="BS38" s="38"/>
+    </row>
+    <row r="39" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39"/>
+      <c r="S39" s="41"/>
+      <c r="Z39" s="38"/>
+      <c r="AB39" s="38"/>
+      <c r="AD39" s="38"/>
+      <c r="AE39"/>
+      <c r="AF39" s="41"/>
+      <c r="AG39" s="21"/>
+      <c r="AM39" s="38"/>
+      <c r="AO39" s="38"/>
+      <c r="AQ39" s="38"/>
+      <c r="AR39"/>
+      <c r="AS39" s="41"/>
+      <c r="AT39" s="21"/>
+      <c r="AZ39" s="38"/>
+      <c r="BB39" s="38"/>
+      <c r="BD39" s="38"/>
+      <c r="BE39"/>
+      <c r="BF39" s="41"/>
+      <c r="BM39" s="38"/>
+      <c r="BO39" s="38"/>
+      <c r="BQ39" s="38"/>
+      <c r="BR39"/>
+      <c r="BS39" s="38"/>
+    </row>
+    <row r="40" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M40" s="38"/>
+      <c r="O40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40"/>
+      <c r="S40" s="41"/>
+      <c r="Z40" s="38"/>
+      <c r="AB40" s="38"/>
+      <c r="AD40" s="38"/>
+      <c r="AE40"/>
+      <c r="AF40" s="41"/>
+      <c r="AG40" s="21"/>
+      <c r="AM40" s="38"/>
+      <c r="AO40" s="38"/>
+      <c r="AQ40" s="38"/>
+      <c r="AR40"/>
+      <c r="AS40" s="41"/>
+      <c r="AT40" s="21"/>
+      <c r="AZ40" s="38"/>
+      <c r="BB40" s="38"/>
+      <c r="BD40" s="38"/>
+      <c r="BE40"/>
+      <c r="BF40" s="41"/>
+      <c r="BM40" s="38"/>
+      <c r="BO40" s="38"/>
+      <c r="BQ40" s="38"/>
+      <c r="BR40"/>
+      <c r="BS40" s="38"/>
+    </row>
+    <row r="41" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="Q41" s="38"/>
+      <c r="R41"/>
+      <c r="S41" s="41"/>
+      <c r="Z41" s="38"/>
+      <c r="AB41" s="38"/>
+      <c r="AD41" s="38"/>
+      <c r="AE41"/>
+      <c r="AF41" s="41"/>
+      <c r="AG41" s="21"/>
+      <c r="AM41" s="38"/>
+      <c r="AO41" s="38"/>
+      <c r="AQ41" s="38"/>
+      <c r="AR41"/>
+      <c r="AS41" s="41"/>
+      <c r="AT41" s="21"/>
+      <c r="AZ41" s="38"/>
+      <c r="BB41" s="38"/>
+      <c r="BD41" s="38"/>
+      <c r="BE41"/>
+      <c r="BF41" s="41"/>
+      <c r="BM41" s="38"/>
+      <c r="BO41" s="38"/>
+      <c r="BQ41" s="38"/>
+      <c r="BR41"/>
+      <c r="BS41" s="38"/>
+    </row>
+    <row r="42" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="Q42" s="38"/>
+      <c r="R42"/>
+      <c r="S42" s="41"/>
+      <c r="Z42" s="38"/>
+      <c r="AB42" s="38"/>
+      <c r="AD42" s="38"/>
+      <c r="AE42"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="21"/>
+      <c r="AM42" s="38"/>
+      <c r="AO42" s="38"/>
+      <c r="AQ42" s="38"/>
+      <c r="AR42"/>
+      <c r="AS42" s="41"/>
+      <c r="AT42" s="21"/>
+      <c r="AZ42" s="38"/>
+      <c r="BB42" s="38"/>
+      <c r="BD42" s="38"/>
+      <c r="BE42"/>
+      <c r="BF42" s="41"/>
+      <c r="BM42" s="38"/>
+      <c r="BO42" s="38"/>
+      <c r="BQ42" s="38"/>
+      <c r="BR42"/>
+      <c r="BS42" s="38"/>
+    </row>
+    <row r="43" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43"/>
+      <c r="S43" s="41"/>
+      <c r="Z43" s="38"/>
+      <c r="AB43" s="38"/>
+      <c r="AD43" s="38"/>
+      <c r="AE43"/>
+      <c r="AF43" s="41"/>
+      <c r="AG43" s="21"/>
+      <c r="AM43" s="38"/>
+      <c r="AO43" s="38"/>
+      <c r="AQ43" s="38"/>
+      <c r="AR43"/>
+      <c r="AS43" s="41"/>
+      <c r="AT43" s="21"/>
+      <c r="AZ43" s="38"/>
+      <c r="BB43" s="38"/>
+      <c r="BD43" s="38"/>
+      <c r="BE43"/>
+      <c r="BF43" s="41"/>
+      <c r="BM43" s="38"/>
+      <c r="BO43" s="38"/>
+      <c r="BQ43" s="38"/>
+      <c r="BR43"/>
+      <c r="BS43" s="38"/>
+    </row>
+    <row r="44" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44"/>
+      <c r="S44" s="41"/>
+      <c r="Z44" s="38"/>
+      <c r="AB44" s="38"/>
+      <c r="AD44" s="38"/>
+      <c r="AE44"/>
+      <c r="AF44" s="41"/>
+      <c r="AG44" s="21"/>
+      <c r="AM44" s="38"/>
+      <c r="AO44" s="38"/>
+      <c r="AQ44" s="38"/>
+      <c r="AR44"/>
+      <c r="AS44" s="41"/>
+      <c r="AT44" s="21"/>
+      <c r="AZ44" s="38"/>
+      <c r="BB44" s="38"/>
+      <c r="BD44" s="38"/>
+      <c r="BE44"/>
+      <c r="BF44" s="41"/>
+      <c r="BM44" s="38"/>
+      <c r="BO44" s="38"/>
+      <c r="BQ44" s="38"/>
+      <c r="BR44"/>
+      <c r="BS44" s="38"/>
+    </row>
+    <row r="45" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="Q45" s="38"/>
+      <c r="R45"/>
+      <c r="S45" s="41"/>
+      <c r="Z45" s="38"/>
+      <c r="AB45" s="38"/>
+      <c r="AD45" s="38"/>
+      <c r="AE45"/>
+      <c r="AF45" s="41"/>
+      <c r="AG45" s="21"/>
+      <c r="AM45" s="38"/>
+      <c r="AO45" s="38"/>
+      <c r="AQ45" s="38"/>
+      <c r="AR45"/>
+      <c r="AS45" s="41"/>
+      <c r="AT45" s="21"/>
+      <c r="AZ45" s="38"/>
+      <c r="BB45" s="38"/>
+      <c r="BD45" s="38"/>
+      <c r="BE45"/>
+      <c r="BF45" s="41"/>
+      <c r="BM45" s="38"/>
+      <c r="BO45" s="38"/>
+      <c r="BQ45" s="38"/>
+      <c r="BR45"/>
+      <c r="BS45" s="38"/>
+    </row>
+    <row r="46" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46"/>
+      <c r="S46" s="41"/>
+      <c r="Z46" s="38"/>
+      <c r="AB46" s="38"/>
+      <c r="AD46" s="38"/>
+      <c r="AE46"/>
+      <c r="AF46" s="41"/>
+      <c r="AG46" s="21"/>
+      <c r="AM46" s="38"/>
+      <c r="AO46" s="38"/>
+      <c r="AQ46" s="38"/>
+      <c r="AR46"/>
+      <c r="AS46" s="41"/>
+      <c r="AT46" s="21"/>
+      <c r="AZ46" s="38"/>
+      <c r="BB46" s="38"/>
+      <c r="BD46" s="38"/>
+      <c r="BE46"/>
+      <c r="BF46" s="41"/>
+      <c r="BM46" s="38"/>
+      <c r="BO46" s="38"/>
+      <c r="BQ46" s="38"/>
+      <c r="BR46"/>
+      <c r="BS46" s="38"/>
+    </row>
+    <row r="47" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M47" s="38"/>
+      <c r="O47" s="38"/>
+      <c r="Q47" s="38"/>
+      <c r="R47"/>
+      <c r="S47" s="41"/>
+      <c r="Z47" s="38"/>
+      <c r="AB47" s="38"/>
+      <c r="AD47" s="38"/>
+      <c r="AE47"/>
+      <c r="AF47" s="41"/>
+      <c r="AG47" s="21"/>
+      <c r="AM47" s="38"/>
+      <c r="AO47" s="38"/>
+      <c r="AQ47" s="38"/>
+      <c r="AR47"/>
+      <c r="AS47" s="41"/>
+      <c r="AT47" s="21"/>
+      <c r="AZ47" s="38"/>
+      <c r="BB47" s="38"/>
+      <c r="BD47" s="38"/>
+      <c r="BE47"/>
+      <c r="BF47" s="41"/>
+      <c r="BM47" s="38"/>
+      <c r="BO47" s="38"/>
+      <c r="BQ47" s="38"/>
+      <c r="BR47"/>
+      <c r="BS47" s="38"/>
+    </row>
+    <row r="48" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M48" s="38"/>
+      <c r="O48" s="38"/>
+      <c r="Q48" s="38"/>
+      <c r="R48"/>
+      <c r="S48" s="41"/>
+      <c r="Z48" s="38"/>
+      <c r="AB48" s="38"/>
+      <c r="AD48" s="38"/>
+      <c r="AE48"/>
+      <c r="AF48" s="41"/>
+      <c r="AG48" s="21"/>
+      <c r="AM48" s="38"/>
+      <c r="AO48" s="38"/>
+      <c r="AQ48" s="38"/>
+      <c r="AR48"/>
+      <c r="AS48" s="41"/>
+      <c r="AT48" s="21"/>
+      <c r="AZ48" s="38"/>
+      <c r="BB48" s="38"/>
+      <c r="BD48" s="38"/>
+      <c r="BE48"/>
+      <c r="BF48" s="41"/>
+      <c r="BM48" s="38"/>
+      <c r="BO48" s="38"/>
+      <c r="BQ48" s="38"/>
+      <c r="BR48"/>
+      <c r="BS48" s="38"/>
+    </row>
+    <row r="49" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M49" s="38"/>
+      <c r="O49" s="38"/>
+      <c r="Q49" s="38"/>
+      <c r="R49"/>
+      <c r="S49" s="41"/>
+      <c r="Z49" s="38"/>
+      <c r="AB49" s="38"/>
+      <c r="AD49" s="38"/>
+      <c r="AE49"/>
+      <c r="AF49" s="41"/>
+      <c r="AG49" s="21"/>
+      <c r="AM49" s="38"/>
+      <c r="AO49" s="38"/>
+      <c r="AQ49" s="38"/>
+      <c r="AR49"/>
+      <c r="AS49" s="41"/>
+      <c r="AT49" s="21"/>
+      <c r="AZ49" s="38"/>
+      <c r="BB49" s="38"/>
+      <c r="BD49" s="38"/>
+      <c r="BE49"/>
+      <c r="BF49" s="41"/>
+      <c r="BM49" s="38"/>
+      <c r="BO49" s="38"/>
+      <c r="BQ49" s="38"/>
+      <c r="BR49"/>
+      <c r="BS49" s="38"/>
+    </row>
+    <row r="50" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50"/>
+      <c r="S50" s="41"/>
+      <c r="Z50" s="38"/>
+      <c r="AB50" s="38"/>
+      <c r="AD50" s="38"/>
+      <c r="AE50"/>
+      <c r="AF50" s="41"/>
+      <c r="AG50" s="21"/>
+      <c r="AM50" s="38"/>
+      <c r="AO50" s="38"/>
+      <c r="AQ50" s="38"/>
+      <c r="AR50"/>
+      <c r="AS50" s="41"/>
+      <c r="AT50" s="21"/>
+      <c r="AZ50" s="38"/>
+      <c r="BB50" s="38"/>
+      <c r="BD50" s="38"/>
+      <c r="BE50"/>
+      <c r="BF50" s="41"/>
+      <c r="BM50" s="38"/>
+      <c r="BO50" s="38"/>
+      <c r="BQ50" s="38"/>
+      <c r="BR50"/>
+      <c r="BS50" s="38"/>
+    </row>
+    <row r="51" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M51" s="38"/>
+      <c r="O51" s="38"/>
+      <c r="Q51" s="38"/>
+      <c r="R51"/>
+      <c r="S51" s="41"/>
+      <c r="Z51" s="38"/>
+      <c r="AB51" s="38"/>
+      <c r="AD51" s="38"/>
+      <c r="AE51"/>
+      <c r="AF51" s="41"/>
+      <c r="AG51" s="21"/>
+      <c r="AM51" s="38"/>
+      <c r="AO51" s="38"/>
+      <c r="AQ51" s="38"/>
+      <c r="AR51"/>
+      <c r="AS51" s="41"/>
+      <c r="AT51" s="21"/>
+      <c r="AZ51" s="38"/>
+      <c r="BB51" s="38"/>
+      <c r="BD51" s="38"/>
+      <c r="BE51"/>
+      <c r="BF51" s="41"/>
+      <c r="BM51" s="38"/>
+      <c r="BO51" s="38"/>
+      <c r="BQ51" s="38"/>
+      <c r="BR51"/>
+      <c r="BS51" s="38"/>
+    </row>
+    <row r="52" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52"/>
+      <c r="S52" s="41"/>
+      <c r="Z52" s="38"/>
+      <c r="AB52" s="38"/>
+      <c r="AD52" s="38"/>
+      <c r="AE52"/>
+      <c r="AF52" s="41"/>
+      <c r="AG52" s="21"/>
+      <c r="AM52" s="38"/>
+      <c r="AO52" s="38"/>
+      <c r="AQ52" s="38"/>
+      <c r="AR52"/>
+      <c r="AS52" s="41"/>
+      <c r="AT52" s="21"/>
+      <c r="AZ52" s="38"/>
+      <c r="BB52" s="38"/>
+      <c r="BD52" s="38"/>
+      <c r="BE52"/>
+      <c r="BF52" s="41"/>
+      <c r="BM52" s="38"/>
+      <c r="BO52" s="38"/>
+      <c r="BQ52" s="38"/>
+      <c r="BR52"/>
+      <c r="BS52" s="38"/>
+    </row>
+    <row r="53" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53"/>
+      <c r="S53" s="41"/>
+      <c r="Z53" s="38"/>
+      <c r="AB53" s="38"/>
+      <c r="AD53" s="38"/>
+      <c r="AE53"/>
+      <c r="AF53" s="41"/>
+      <c r="AG53" s="21"/>
+      <c r="AM53" s="38"/>
+      <c r="AO53" s="38"/>
+      <c r="AQ53" s="38"/>
+      <c r="AR53"/>
+      <c r="AS53" s="41"/>
+      <c r="AT53" s="21"/>
+      <c r="AZ53" s="38"/>
+      <c r="BB53" s="38"/>
+      <c r="BD53" s="38"/>
+      <c r="BE53"/>
+      <c r="BF53" s="41"/>
+      <c r="BM53" s="38"/>
+      <c r="BO53" s="38"/>
+      <c r="BQ53" s="38"/>
+      <c r="BR53"/>
+      <c r="BS53" s="38"/>
+    </row>
+    <row r="54" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54"/>
+      <c r="S54" s="41"/>
+      <c r="Z54" s="38"/>
+      <c r="AB54" s="38"/>
+      <c r="AD54" s="38"/>
+      <c r="AE54"/>
+      <c r="AF54" s="41"/>
+      <c r="AG54" s="21"/>
+      <c r="AM54" s="38"/>
+      <c r="AO54" s="38"/>
+      <c r="AQ54" s="38"/>
+      <c r="AR54"/>
+      <c r="AS54" s="41"/>
+      <c r="AT54" s="21"/>
+      <c r="AZ54" s="38"/>
+      <c r="BB54" s="38"/>
+      <c r="BD54" s="38"/>
+      <c r="BE54"/>
+      <c r="BF54" s="41"/>
+      <c r="BM54" s="38"/>
+      <c r="BO54" s="38"/>
+      <c r="BQ54" s="38"/>
+      <c r="BR54"/>
+      <c r="BS54" s="38"/>
+    </row>
+    <row r="55" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55"/>
+      <c r="S55" s="41"/>
+      <c r="Z55" s="38"/>
+      <c r="AB55" s="38"/>
+      <c r="AD55" s="38"/>
+      <c r="AE55"/>
+      <c r="AF55" s="41"/>
+      <c r="AG55" s="21"/>
+      <c r="AM55" s="38"/>
+      <c r="AO55" s="38"/>
+      <c r="AQ55" s="38"/>
+      <c r="AR55"/>
+      <c r="AS55" s="41"/>
+      <c r="AT55" s="21"/>
+      <c r="AZ55" s="38"/>
+      <c r="BB55" s="38"/>
+      <c r="BD55" s="38"/>
+      <c r="BE55"/>
+      <c r="BF55" s="41"/>
+      <c r="BM55" s="38"/>
+      <c r="BO55" s="38"/>
+      <c r="BQ55" s="38"/>
+      <c r="BR55"/>
+      <c r="BS55" s="38"/>
+    </row>
+    <row r="56" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M56" s="38"/>
+      <c r="O56" s="38"/>
+      <c r="Q56" s="38"/>
+      <c r="R56"/>
+      <c r="S56" s="41"/>
+      <c r="Z56" s="38"/>
+      <c r="AB56" s="38"/>
+      <c r="AD56" s="38"/>
+      <c r="AE56"/>
+      <c r="AF56" s="41"/>
+      <c r="AG56" s="21"/>
+      <c r="AM56" s="38"/>
+      <c r="AO56" s="38"/>
+      <c r="AQ56" s="38"/>
+      <c r="AR56"/>
+      <c r="AS56" s="41"/>
+      <c r="AT56" s="21"/>
+      <c r="AZ56" s="38"/>
+      <c r="BB56" s="38"/>
+      <c r="BD56" s="38"/>
+      <c r="BE56"/>
+      <c r="BF56" s="41"/>
+      <c r="BM56" s="38"/>
+      <c r="BO56" s="38"/>
+      <c r="BQ56" s="38"/>
+      <c r="BR56"/>
+      <c r="BS56" s="38"/>
+    </row>
+    <row r="57" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57"/>
+      <c r="S57" s="41"/>
+      <c r="Z57" s="38"/>
+      <c r="AB57" s="38"/>
+      <c r="AD57" s="38"/>
+      <c r="AE57"/>
+      <c r="AF57" s="41"/>
+      <c r="AG57" s="21"/>
+      <c r="AM57" s="38"/>
+      <c r="AO57" s="38"/>
+      <c r="AQ57" s="38"/>
+      <c r="AR57"/>
+      <c r="AS57" s="41"/>
+      <c r="AT57" s="21"/>
+      <c r="AZ57" s="38"/>
+      <c r="BB57" s="38"/>
+      <c r="BD57" s="38"/>
+      <c r="BE57"/>
+      <c r="BF57" s="41"/>
+      <c r="BM57" s="38"/>
+      <c r="BO57" s="38"/>
+      <c r="BQ57" s="38"/>
+      <c r="BR57"/>
+      <c r="BS57" s="38"/>
+    </row>
+    <row r="58" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M58" s="38"/>
+      <c r="O58" s="38"/>
+      <c r="Q58" s="38"/>
+      <c r="R58"/>
+      <c r="S58" s="41"/>
+      <c r="Z58" s="38"/>
+      <c r="AB58" s="38"/>
+      <c r="AD58" s="38"/>
+      <c r="AE58"/>
+      <c r="AF58" s="41"/>
+      <c r="AG58" s="21"/>
+      <c r="AM58" s="38"/>
+      <c r="AO58" s="38"/>
+      <c r="AQ58" s="38"/>
+      <c r="AR58"/>
+      <c r="AS58" s="41"/>
+      <c r="AT58" s="21"/>
+      <c r="AZ58" s="38"/>
+      <c r="BB58" s="38"/>
+      <c r="BD58" s="38"/>
+      <c r="BE58"/>
+      <c r="BF58" s="41"/>
+      <c r="BM58" s="38"/>
+      <c r="BO58" s="38"/>
+      <c r="BQ58" s="38"/>
+      <c r="BR58"/>
+      <c r="BS58" s="38"/>
+    </row>
+    <row r="59" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M59" s="38"/>
+      <c r="O59" s="38"/>
+      <c r="Q59" s="38"/>
+      <c r="R59"/>
+      <c r="S59" s="41"/>
+      <c r="Z59" s="38"/>
+      <c r="AB59" s="38"/>
+      <c r="AD59" s="38"/>
+      <c r="AE59"/>
+      <c r="AF59" s="41"/>
+      <c r="AG59" s="21"/>
+      <c r="AM59" s="38"/>
+      <c r="AO59" s="38"/>
+      <c r="AQ59" s="38"/>
+      <c r="AR59"/>
+      <c r="AS59" s="41"/>
+      <c r="AT59" s="21"/>
+      <c r="AZ59" s="38"/>
+      <c r="BB59" s="38"/>
+      <c r="BD59" s="38"/>
+      <c r="BE59"/>
+      <c r="BF59" s="41"/>
+      <c r="BM59" s="38"/>
+      <c r="BO59" s="38"/>
+      <c r="BQ59" s="38"/>
+      <c r="BR59"/>
+      <c r="BS59" s="38"/>
+    </row>
+    <row r="60" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M60" s="38"/>
+      <c r="O60" s="38"/>
+      <c r="Q60" s="38"/>
+      <c r="R60"/>
+      <c r="S60" s="41"/>
+      <c r="Z60" s="38"/>
+      <c r="AB60" s="38"/>
+      <c r="AD60" s="38"/>
+      <c r="AE60"/>
+      <c r="AF60" s="41"/>
+      <c r="AG60" s="21"/>
+      <c r="AM60" s="38"/>
+      <c r="AO60" s="38"/>
+      <c r="AQ60" s="38"/>
+      <c r="AR60"/>
+      <c r="AS60" s="41"/>
+      <c r="AT60" s="21"/>
+      <c r="AZ60" s="38"/>
+      <c r="BB60" s="38"/>
+      <c r="BD60" s="38"/>
+      <c r="BE60"/>
+      <c r="BF60" s="41"/>
+      <c r="BM60" s="38"/>
+      <c r="BO60" s="38"/>
+      <c r="BQ60" s="38"/>
+      <c r="BR60"/>
+      <c r="BS60" s="38"/>
+    </row>
+    <row r="61" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M61" s="38"/>
+      <c r="O61" s="38"/>
+      <c r="Q61" s="38"/>
+      <c r="R61"/>
+      <c r="S61" s="41"/>
+      <c r="Z61" s="38"/>
+      <c r="AB61" s="38"/>
+      <c r="AD61" s="38"/>
+      <c r="AE61"/>
+      <c r="AF61" s="41"/>
+      <c r="AG61" s="21"/>
+      <c r="AM61" s="38"/>
+      <c r="AO61" s="38"/>
+      <c r="AQ61" s="38"/>
+      <c r="AR61"/>
+      <c r="AS61" s="41"/>
+      <c r="AT61" s="21"/>
+      <c r="AZ61" s="38"/>
+      <c r="BB61" s="38"/>
+      <c r="BD61" s="38"/>
+      <c r="BE61"/>
+      <c r="BF61" s="41"/>
+      <c r="BM61" s="38"/>
+      <c r="BO61" s="38"/>
+      <c r="BQ61" s="38"/>
+      <c r="BR61"/>
+      <c r="BS61" s="38"/>
+    </row>
+    <row r="62" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M62" s="38"/>
+      <c r="O62" s="38"/>
+      <c r="Q62" s="38"/>
+      <c r="R62"/>
+      <c r="S62" s="41"/>
+      <c r="Z62" s="38"/>
+      <c r="AB62" s="38"/>
+      <c r="AD62" s="38"/>
+      <c r="AE62"/>
+      <c r="AF62" s="41"/>
+      <c r="AG62" s="21"/>
+      <c r="AM62" s="38"/>
+      <c r="AO62" s="38"/>
+      <c r="AQ62" s="38"/>
+      <c r="AR62"/>
+      <c r="AS62" s="41"/>
+      <c r="AT62" s="21"/>
+      <c r="AZ62" s="38"/>
+      <c r="BB62" s="38"/>
+      <c r="BD62" s="38"/>
+      <c r="BE62"/>
+      <c r="BF62" s="41"/>
+      <c r="BM62" s="38"/>
+      <c r="BO62" s="38"/>
+      <c r="BQ62" s="38"/>
+      <c r="BR62"/>
+      <c r="BS62" s="38"/>
+    </row>
+    <row r="63" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M63" s="38"/>
+      <c r="O63" s="38"/>
+      <c r="Q63" s="38"/>
+      <c r="R63"/>
+      <c r="S63" s="41"/>
+      <c r="Z63" s="38"/>
+      <c r="AB63" s="38"/>
+      <c r="AD63" s="38"/>
+      <c r="AE63"/>
+      <c r="AF63" s="41"/>
+      <c r="AG63" s="21"/>
+      <c r="AM63" s="38"/>
+      <c r="AO63" s="38"/>
+      <c r="AQ63" s="38"/>
+      <c r="AR63"/>
+      <c r="AS63" s="41"/>
+      <c r="AT63" s="21"/>
+      <c r="AZ63" s="38"/>
+      <c r="BB63" s="38"/>
+      <c r="BD63" s="38"/>
+      <c r="BE63"/>
+      <c r="BF63" s="41"/>
+      <c r="BM63" s="38"/>
+      <c r="BO63" s="38"/>
+      <c r="BQ63" s="38"/>
+      <c r="BR63"/>
+      <c r="BS63" s="38"/>
+    </row>
+    <row r="64" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M64" s="38"/>
+      <c r="O64" s="38"/>
+      <c r="Q64" s="38"/>
+      <c r="R64"/>
+      <c r="S64" s="41"/>
+      <c r="Z64" s="38"/>
+      <c r="AB64" s="38"/>
+      <c r="AD64" s="38"/>
+      <c r="AE64"/>
+      <c r="AF64" s="41"/>
+      <c r="AG64" s="21"/>
+      <c r="AM64" s="38"/>
+      <c r="AO64" s="38"/>
+      <c r="AQ64" s="38"/>
+      <c r="AR64"/>
+      <c r="AS64" s="41"/>
+      <c r="AT64" s="21"/>
+      <c r="AZ64" s="38"/>
+      <c r="BB64" s="38"/>
+      <c r="BD64" s="38"/>
+      <c r="BE64"/>
+      <c r="BF64" s="41"/>
+      <c r="BM64" s="38"/>
+      <c r="BO64" s="38"/>
+      <c r="BQ64" s="38"/>
+      <c r="BR64"/>
+      <c r="BS64" s="38"/>
+    </row>
+    <row r="65" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M65" s="38"/>
+      <c r="O65" s="38"/>
+      <c r="Q65" s="38"/>
+      <c r="R65"/>
+      <c r="S65" s="41"/>
+      <c r="Z65" s="38"/>
+      <c r="AB65" s="38"/>
+      <c r="AD65" s="38"/>
+      <c r="AE65"/>
+      <c r="AF65" s="41"/>
+      <c r="AG65" s="21"/>
+      <c r="AM65" s="38"/>
+      <c r="AO65" s="38"/>
+      <c r="AQ65" s="38"/>
+      <c r="AR65"/>
+      <c r="AS65" s="41"/>
+      <c r="AT65" s="21"/>
+      <c r="AZ65" s="38"/>
+      <c r="BB65" s="38"/>
+      <c r="BD65" s="38"/>
+      <c r="BE65"/>
+      <c r="BF65" s="41"/>
+      <c r="BM65" s="38"/>
+      <c r="BO65" s="38"/>
+      <c r="BQ65" s="38"/>
+      <c r="BR65"/>
+      <c r="BS65" s="38"/>
+    </row>
+    <row r="66" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M66" s="38"/>
+      <c r="O66" s="38"/>
+      <c r="Q66" s="38"/>
+      <c r="R66"/>
+      <c r="S66" s="41"/>
+      <c r="Z66" s="38"/>
+      <c r="AB66" s="38"/>
+      <c r="AD66" s="38"/>
+      <c r="AE66"/>
+      <c r="AF66" s="41"/>
+      <c r="AG66" s="21"/>
+      <c r="AM66" s="38"/>
+      <c r="AO66" s="38"/>
+      <c r="AQ66" s="38"/>
+      <c r="AR66"/>
+      <c r="AS66" s="41"/>
+      <c r="AT66" s="21"/>
+      <c r="AZ66" s="38"/>
+      <c r="BB66" s="38"/>
+      <c r="BD66" s="38"/>
+      <c r="BE66"/>
+      <c r="BF66" s="41"/>
+      <c r="BM66" s="38"/>
+      <c r="BO66" s="38"/>
+      <c r="BQ66" s="38"/>
+      <c r="BR66"/>
+      <c r="BS66" s="38"/>
+    </row>
+    <row r="67" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M67" s="38"/>
+      <c r="O67" s="38"/>
+      <c r="Q67" s="38"/>
+      <c r="R67"/>
+      <c r="S67" s="41"/>
+      <c r="Z67" s="38"/>
+      <c r="AB67" s="38"/>
+      <c r="AD67" s="38"/>
+      <c r="AE67"/>
+      <c r="AF67" s="41"/>
+      <c r="AG67" s="21"/>
+      <c r="AM67" s="38"/>
+      <c r="AO67" s="38"/>
+      <c r="AQ67" s="38"/>
+      <c r="AR67"/>
+      <c r="AS67" s="41"/>
+      <c r="AT67" s="21"/>
+      <c r="AZ67" s="38"/>
+      <c r="BB67" s="38"/>
+      <c r="BD67" s="38"/>
+      <c r="BE67"/>
+      <c r="BF67" s="41"/>
+      <c r="BM67" s="38"/>
+      <c r="BO67" s="38"/>
+      <c r="BQ67" s="38"/>
+      <c r="BR67"/>
+      <c r="BS67" s="38"/>
+    </row>
+    <row r="68" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M68" s="38"/>
+      <c r="O68" s="38"/>
+      <c r="Q68" s="38"/>
+      <c r="R68"/>
+      <c r="S68" s="41"/>
+      <c r="Z68" s="38"/>
+      <c r="AB68" s="38"/>
+      <c r="AD68" s="38"/>
+      <c r="AE68"/>
+      <c r="AF68" s="41"/>
+      <c r="AG68" s="21"/>
+      <c r="AM68" s="38"/>
+      <c r="AO68" s="38"/>
+      <c r="AQ68" s="38"/>
+      <c r="AR68"/>
+      <c r="AS68" s="41"/>
+      <c r="AT68" s="21"/>
+      <c r="AZ68" s="38"/>
+      <c r="BB68" s="38"/>
+      <c r="BD68" s="38"/>
+      <c r="BE68"/>
+      <c r="BF68" s="41"/>
+      <c r="BM68" s="38"/>
+      <c r="BO68" s="38"/>
+      <c r="BQ68" s="38"/>
+      <c r="BR68"/>
+      <c r="BS68" s="38"/>
+    </row>
+    <row r="69" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M69" s="38"/>
+      <c r="O69" s="38"/>
+      <c r="Q69" s="38"/>
+      <c r="R69"/>
+      <c r="S69" s="41"/>
+      <c r="Z69" s="38"/>
+      <c r="AB69" s="38"/>
+      <c r="AD69" s="38"/>
+      <c r="AE69"/>
+      <c r="AF69" s="41"/>
+      <c r="AG69" s="21"/>
+      <c r="AM69" s="38"/>
+      <c r="AO69" s="38"/>
+      <c r="AQ69" s="38"/>
+      <c r="AR69"/>
+      <c r="AS69" s="41"/>
+      <c r="AT69" s="21"/>
+      <c r="AZ69" s="38"/>
+      <c r="BB69" s="38"/>
+      <c r="BD69" s="38"/>
+      <c r="BE69"/>
+      <c r="BF69" s="41"/>
+      <c r="BM69" s="38"/>
+      <c r="BO69" s="38"/>
+      <c r="BQ69" s="38"/>
+      <c r="BR69"/>
+      <c r="BS69" s="38"/>
+    </row>
+    <row r="70" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="Q70" s="38"/>
+      <c r="R70"/>
+      <c r="S70" s="41"/>
+      <c r="Z70" s="38"/>
+      <c r="AB70" s="38"/>
+      <c r="AD70" s="38"/>
+      <c r="AE70"/>
+      <c r="AF70" s="41"/>
+      <c r="AG70" s="21"/>
+      <c r="AM70" s="38"/>
+      <c r="AO70" s="38"/>
+      <c r="AQ70" s="38"/>
+      <c r="AR70"/>
+      <c r="AS70" s="41"/>
+      <c r="AT70" s="21"/>
+      <c r="AZ70" s="38"/>
+      <c r="BB70" s="38"/>
+      <c r="BD70" s="38"/>
+      <c r="BE70"/>
+      <c r="BF70" s="41"/>
+      <c r="BM70" s="38"/>
+      <c r="BO70" s="38"/>
+      <c r="BQ70" s="38"/>
+      <c r="BR70"/>
+      <c r="BS70" s="38"/>
+    </row>
+    <row r="71" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M71" s="38"/>
+      <c r="O71" s="38"/>
+      <c r="Q71" s="38"/>
+      <c r="R71"/>
+      <c r="S71" s="41"/>
+      <c r="Z71" s="38"/>
+      <c r="AB71" s="38"/>
+      <c r="AD71" s="38"/>
+      <c r="AE71"/>
+      <c r="AF71" s="41"/>
+      <c r="AG71" s="21"/>
+      <c r="AM71" s="38"/>
+      <c r="AO71" s="38"/>
+      <c r="AQ71" s="38"/>
+      <c r="AR71"/>
+      <c r="AS71" s="41"/>
+      <c r="AT71" s="21"/>
+      <c r="AZ71" s="38"/>
+      <c r="BB71" s="38"/>
+      <c r="BD71" s="38"/>
+      <c r="BE71"/>
+      <c r="BF71" s="41"/>
+      <c r="BM71" s="38"/>
+      <c r="BO71" s="38"/>
+      <c r="BQ71" s="38"/>
+      <c r="BR71"/>
+      <c r="BS71" s="38"/>
+    </row>
+    <row r="72" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M72" s="38"/>
+      <c r="O72" s="38"/>
+      <c r="Q72" s="38"/>
+      <c r="R72"/>
+      <c r="S72" s="41"/>
+      <c r="Z72" s="38"/>
+      <c r="AB72" s="38"/>
+      <c r="AD72" s="38"/>
+      <c r="AE72"/>
+      <c r="AF72" s="41"/>
+      <c r="AG72" s="21"/>
+      <c r="AM72" s="38"/>
+      <c r="AO72" s="38"/>
+      <c r="AQ72" s="38"/>
+      <c r="AR72"/>
+      <c r="AS72" s="41"/>
+      <c r="AT72" s="21"/>
+      <c r="AZ72" s="38"/>
+      <c r="BB72" s="38"/>
+      <c r="BD72" s="38"/>
+      <c r="BE72"/>
+      <c r="BF72" s="41"/>
+      <c r="BM72" s="38"/>
+      <c r="BO72" s="38"/>
+      <c r="BQ72" s="38"/>
+      <c r="BR72"/>
+      <c r="BS72" s="38"/>
+    </row>
+    <row r="73" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M73" s="38"/>
+      <c r="O73" s="38"/>
+      <c r="Q73" s="38"/>
+      <c r="R73"/>
+      <c r="S73" s="41"/>
+      <c r="Z73" s="38"/>
+      <c r="AB73" s="38"/>
+      <c r="AD73" s="38"/>
+      <c r="AE73"/>
+      <c r="AF73" s="41"/>
+      <c r="AG73" s="21"/>
+      <c r="AM73" s="38"/>
+      <c r="AO73" s="38"/>
+      <c r="AQ73" s="38"/>
+      <c r="AR73"/>
+      <c r="AS73" s="41"/>
+      <c r="AT73" s="21"/>
+      <c r="AZ73" s="38"/>
+      <c r="BB73" s="38"/>
+      <c r="BD73" s="38"/>
+      <c r="BE73"/>
+      <c r="BF73" s="41"/>
+      <c r="BM73" s="38"/>
+      <c r="BO73" s="38"/>
+      <c r="BQ73" s="38"/>
+      <c r="BR73"/>
+      <c r="BS73" s="38"/>
+    </row>
+    <row r="74" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M74" s="38"/>
+      <c r="O74" s="38"/>
+      <c r="Q74" s="38"/>
+      <c r="R74"/>
+      <c r="S74" s="41"/>
+      <c r="Z74" s="38"/>
+      <c r="AB74" s="38"/>
+      <c r="AD74" s="38"/>
+      <c r="AE74"/>
+      <c r="AF74" s="41"/>
+      <c r="AG74" s="21"/>
+      <c r="AM74" s="38"/>
+      <c r="AO74" s="38"/>
+      <c r="AQ74" s="38"/>
+      <c r="AR74"/>
+      <c r="AS74" s="41"/>
+      <c r="AT74" s="21"/>
+      <c r="AZ74" s="38"/>
+      <c r="BB74" s="38"/>
+      <c r="BD74" s="38"/>
+      <c r="BE74"/>
+      <c r="BF74" s="41"/>
+      <c r="BM74" s="38"/>
+      <c r="BO74" s="38"/>
+      <c r="BQ74" s="38"/>
+      <c r="BR74"/>
+      <c r="BS74" s="38"/>
+    </row>
+    <row r="75" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M75" s="38"/>
+      <c r="O75" s="38"/>
+      <c r="Q75" s="38"/>
+      <c r="R75"/>
+      <c r="S75" s="41"/>
+      <c r="Z75" s="38"/>
+      <c r="AB75" s="38"/>
+      <c r="AD75" s="38"/>
+      <c r="AE75"/>
+      <c r="AF75" s="41"/>
+      <c r="AG75" s="21"/>
+      <c r="AM75" s="38"/>
+      <c r="AO75" s="38"/>
+      <c r="AQ75" s="38"/>
+      <c r="AR75"/>
+      <c r="AS75" s="41"/>
+      <c r="AT75" s="21"/>
+      <c r="AZ75" s="38"/>
+      <c r="BB75" s="38"/>
+      <c r="BD75" s="38"/>
+      <c r="BE75"/>
+      <c r="BF75" s="41"/>
+      <c r="BM75" s="38"/>
+      <c r="BO75" s="38"/>
+      <c r="BQ75" s="38"/>
+      <c r="BR75"/>
+      <c r="BS75" s="38"/>
+    </row>
+    <row r="76" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M76" s="38"/>
+      <c r="O76" s="38"/>
+      <c r="Q76" s="38"/>
+      <c r="R76"/>
+      <c r="S76" s="41"/>
+      <c r="Z76" s="38"/>
+      <c r="AB76" s="38"/>
+      <c r="AD76" s="38"/>
+      <c r="AE76"/>
+      <c r="AF76" s="41"/>
+      <c r="AG76" s="21"/>
+      <c r="AM76" s="38"/>
+      <c r="AO76" s="38"/>
+      <c r="AQ76" s="38"/>
+      <c r="AR76"/>
+      <c r="AS76" s="41"/>
+      <c r="AT76" s="21"/>
+      <c r="AZ76" s="38"/>
+      <c r="BB76" s="38"/>
+      <c r="BD76" s="38"/>
+      <c r="BE76"/>
+      <c r="BF76" s="41"/>
+      <c r="BM76" s="38"/>
+      <c r="BO76" s="38"/>
+      <c r="BQ76" s="38"/>
+      <c r="BR76"/>
+      <c r="BS76" s="38"/>
+    </row>
+    <row r="77" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M77" s="38"/>
+      <c r="O77" s="38"/>
+      <c r="Q77" s="38"/>
+      <c r="R77"/>
+      <c r="S77" s="41"/>
+      <c r="Z77" s="38"/>
+      <c r="AB77" s="38"/>
+      <c r="AD77" s="38"/>
+      <c r="AE77"/>
+      <c r="AF77" s="41"/>
+      <c r="AG77" s="21"/>
+      <c r="AM77" s="38"/>
+      <c r="AO77" s="38"/>
+      <c r="AQ77" s="38"/>
+      <c r="AR77"/>
+      <c r="AS77" s="41"/>
+      <c r="AT77" s="21"/>
+      <c r="AZ77" s="38"/>
+      <c r="BB77" s="38"/>
+      <c r="BD77" s="38"/>
+      <c r="BE77"/>
+      <c r="BF77" s="41"/>
+      <c r="BM77" s="38"/>
+      <c r="BO77" s="38"/>
+      <c r="BQ77" s="38"/>
+      <c r="BR77"/>
+      <c r="BS77" s="38"/>
+    </row>
+    <row r="78" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M78" s="38"/>
+      <c r="O78" s="38"/>
+      <c r="Q78" s="38"/>
+      <c r="R78"/>
+      <c r="S78" s="41"/>
+      <c r="Z78" s="38"/>
+      <c r="AB78" s="38"/>
+      <c r="AD78" s="38"/>
+      <c r="AE78"/>
+      <c r="AF78" s="41"/>
+      <c r="AG78" s="21"/>
+      <c r="AM78" s="38"/>
+      <c r="AO78" s="38"/>
+      <c r="AQ78" s="38"/>
+      <c r="AR78"/>
+      <c r="AS78" s="41"/>
+      <c r="AT78" s="21"/>
+      <c r="AZ78" s="38"/>
+      <c r="BB78" s="38"/>
+      <c r="BD78" s="38"/>
+      <c r="BE78"/>
+      <c r="BF78" s="41"/>
+      <c r="BM78" s="38"/>
+      <c r="BO78" s="38"/>
+      <c r="BQ78" s="38"/>
+      <c r="BR78"/>
+      <c r="BS78" s="38"/>
+    </row>
+    <row r="79" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M79" s="38"/>
+      <c r="O79" s="38"/>
+      <c r="Q79" s="38"/>
+      <c r="R79"/>
+      <c r="S79" s="41"/>
+      <c r="Z79" s="38"/>
+      <c r="AB79" s="38"/>
+      <c r="AD79" s="38"/>
+      <c r="AE79"/>
+      <c r="AF79" s="41"/>
+      <c r="AG79" s="21"/>
+      <c r="AM79" s="38"/>
+      <c r="AO79" s="38"/>
+      <c r="AQ79" s="38"/>
+      <c r="AR79"/>
+      <c r="AS79" s="41"/>
+      <c r="AT79" s="21"/>
+      <c r="AZ79" s="38"/>
+      <c r="BB79" s="38"/>
+      <c r="BD79" s="38"/>
+      <c r="BE79"/>
+      <c r="BF79" s="41"/>
+      <c r="BM79" s="38"/>
+      <c r="BO79" s="38"/>
+      <c r="BQ79" s="38"/>
+      <c r="BR79"/>
+      <c r="BS79" s="38"/>
+    </row>
+    <row r="80" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M80" s="38"/>
+      <c r="O80" s="38"/>
+      <c r="Q80" s="38"/>
+      <c r="R80"/>
+      <c r="S80" s="41"/>
+      <c r="Z80" s="38"/>
+      <c r="AB80" s="38"/>
+      <c r="AD80" s="38"/>
+      <c r="AE80"/>
+      <c r="AF80" s="41"/>
+      <c r="AG80" s="21"/>
+      <c r="AM80" s="38"/>
+      <c r="AO80" s="38"/>
+      <c r="AQ80" s="38"/>
+      <c r="AR80"/>
+      <c r="AS80" s="41"/>
+      <c r="AT80" s="21"/>
+      <c r="AZ80" s="38"/>
+      <c r="BB80" s="38"/>
+      <c r="BD80" s="38"/>
+      <c r="BE80"/>
+      <c r="BF80" s="41"/>
+      <c r="BM80" s="38"/>
+      <c r="BO80" s="38"/>
+      <c r="BQ80" s="38"/>
+      <c r="BR80"/>
+      <c r="BS80" s="38"/>
+    </row>
+    <row r="81" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M81" s="38"/>
+      <c r="O81" s="38"/>
+      <c r="Q81" s="38"/>
+      <c r="R81"/>
+      <c r="S81" s="41"/>
+      <c r="Z81" s="38"/>
+      <c r="AB81" s="38"/>
+      <c r="AD81" s="38"/>
+      <c r="AE81"/>
+      <c r="AF81" s="41"/>
+      <c r="AG81" s="21"/>
+      <c r="AM81" s="38"/>
+      <c r="AO81" s="38"/>
+      <c r="AQ81" s="38"/>
+      <c r="AR81"/>
+      <c r="AS81" s="41"/>
+      <c r="AT81" s="21"/>
+      <c r="AZ81" s="38"/>
+      <c r="BB81" s="38"/>
+      <c r="BD81" s="38"/>
+      <c r="BE81"/>
+      <c r="BF81" s="41"/>
+      <c r="BM81" s="38"/>
+      <c r="BO81" s="38"/>
+      <c r="BQ81" s="38"/>
+      <c r="BR81"/>
+      <c r="BS81" s="38"/>
+    </row>
+    <row r="82" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M82" s="38"/>
+      <c r="O82" s="38"/>
+      <c r="Q82" s="38"/>
+      <c r="R82"/>
+      <c r="S82" s="41"/>
+      <c r="Z82" s="38"/>
+      <c r="AB82" s="38"/>
+      <c r="AD82" s="38"/>
+      <c r="AE82"/>
+      <c r="AF82" s="41"/>
+      <c r="AG82" s="21"/>
+      <c r="AM82" s="38"/>
+      <c r="AO82" s="38"/>
+      <c r="AQ82" s="38"/>
+      <c r="AR82"/>
+      <c r="AS82" s="41"/>
+      <c r="AT82" s="21"/>
+      <c r="AZ82" s="38"/>
+      <c r="BB82" s="38"/>
+      <c r="BD82" s="38"/>
+      <c r="BE82"/>
+      <c r="BF82" s="41"/>
+      <c r="BM82" s="38"/>
+      <c r="BO82" s="38"/>
+      <c r="BQ82" s="38"/>
+      <c r="BR82"/>
+      <c r="BS82" s="38"/>
+    </row>
+    <row r="83" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M83" s="38"/>
+      <c r="O83" s="38"/>
+      <c r="Q83" s="38"/>
+      <c r="R83"/>
+      <c r="S83" s="41"/>
+      <c r="Z83" s="38"/>
+      <c r="AB83" s="38"/>
+      <c r="AD83" s="38"/>
+      <c r="AE83"/>
+      <c r="AF83" s="41"/>
+      <c r="AG83" s="21"/>
+      <c r="AM83" s="38"/>
+      <c r="AO83" s="38"/>
+      <c r="AQ83" s="38"/>
+      <c r="AR83"/>
+      <c r="AS83" s="41"/>
+      <c r="AT83" s="21"/>
+      <c r="AZ83" s="38"/>
+      <c r="BB83" s="38"/>
+      <c r="BD83" s="38"/>
+      <c r="BE83"/>
+      <c r="BF83" s="41"/>
+      <c r="BM83" s="38"/>
+      <c r="BO83" s="38"/>
+      <c r="BQ83" s="38"/>
+      <c r="BR83"/>
+      <c r="BS83" s="38"/>
+    </row>
+    <row r="84" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M84" s="38"/>
+      <c r="O84" s="38"/>
+      <c r="Q84" s="38"/>
+      <c r="R84"/>
+      <c r="S84" s="41"/>
+      <c r="Z84" s="38"/>
+      <c r="AB84" s="38"/>
+      <c r="AD84" s="38"/>
+      <c r="AE84"/>
+      <c r="AF84" s="41"/>
+      <c r="AG84" s="21"/>
+      <c r="AM84" s="38"/>
+      <c r="AO84" s="38"/>
+      <c r="AQ84" s="38"/>
+      <c r="AR84"/>
+      <c r="AS84" s="41"/>
+      <c r="AT84" s="21"/>
+      <c r="AZ84" s="38"/>
+      <c r="BB84" s="38"/>
+      <c r="BD84" s="38"/>
+      <c r="BE84"/>
+      <c r="BF84" s="41"/>
+      <c r="BM84" s="38"/>
+      <c r="BO84" s="38"/>
+      <c r="BQ84" s="38"/>
+      <c r="BR84"/>
+      <c r="BS84" s="38"/>
+    </row>
+    <row r="85" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M85" s="38"/>
+      <c r="O85" s="38"/>
+      <c r="Q85" s="38"/>
+      <c r="R85"/>
+      <c r="S85" s="41"/>
+      <c r="Z85" s="38"/>
+      <c r="AB85" s="38"/>
+      <c r="AD85" s="38"/>
+      <c r="AE85"/>
+      <c r="AF85" s="41"/>
+      <c r="AG85" s="21"/>
+      <c r="AM85" s="38"/>
+      <c r="AO85" s="38"/>
+      <c r="AQ85" s="38"/>
+      <c r="AR85"/>
+      <c r="AS85" s="41"/>
+      <c r="AT85" s="21"/>
+      <c r="AZ85" s="38"/>
+      <c r="BB85" s="38"/>
+      <c r="BD85" s="38"/>
+      <c r="BE85"/>
+      <c r="BF85" s="41"/>
+      <c r="BM85" s="38"/>
+      <c r="BO85" s="38"/>
+      <c r="BQ85" s="38"/>
+      <c r="BR85"/>
+      <c r="BS85" s="38"/>
+    </row>
+    <row r="86" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M86" s="38"/>
+      <c r="O86" s="38"/>
+      <c r="Q86" s="38"/>
+      <c r="R86"/>
+      <c r="S86" s="41"/>
+      <c r="Z86" s="38"/>
+      <c r="AB86" s="38"/>
+      <c r="AD86" s="38"/>
+      <c r="AE86"/>
+      <c r="AF86" s="41"/>
+      <c r="AG86" s="21"/>
+      <c r="AM86" s="38"/>
+      <c r="AO86" s="38"/>
+      <c r="AQ86" s="38"/>
+      <c r="AR86"/>
+      <c r="AS86" s="41"/>
+      <c r="AT86" s="21"/>
+      <c r="AZ86" s="38"/>
+      <c r="BB86" s="38"/>
+      <c r="BD86" s="38"/>
+      <c r="BE86"/>
+      <c r="BF86" s="41"/>
+      <c r="BM86" s="38"/>
+      <c r="BO86" s="38"/>
+      <c r="BQ86" s="38"/>
+      <c r="BR86"/>
+      <c r="BS86" s="38"/>
+    </row>
+    <row r="87" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M87" s="38"/>
+      <c r="O87" s="38"/>
+      <c r="Q87" s="38"/>
+      <c r="R87"/>
+      <c r="S87" s="41"/>
+      <c r="Z87" s="38"/>
+      <c r="AB87" s="38"/>
+      <c r="AD87" s="38"/>
+      <c r="AE87"/>
+      <c r="AF87" s="41"/>
+      <c r="AG87" s="21"/>
+      <c r="AM87" s="38"/>
+      <c r="AO87" s="38"/>
+      <c r="AQ87" s="38"/>
+      <c r="AR87"/>
+      <c r="AS87" s="41"/>
+      <c r="AT87" s="21"/>
+      <c r="AZ87" s="38"/>
+      <c r="BB87" s="38"/>
+      <c r="BD87" s="38"/>
+      <c r="BE87"/>
+      <c r="BF87" s="41"/>
+      <c r="BM87" s="38"/>
+      <c r="BO87" s="38"/>
+      <c r="BQ87" s="38"/>
+      <c r="BR87"/>
+      <c r="BS87" s="38"/>
+    </row>
+    <row r="88" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M88" s="38"/>
+      <c r="O88" s="38"/>
+      <c r="Q88" s="38"/>
+      <c r="R88"/>
+      <c r="S88" s="41"/>
+      <c r="Z88" s="38"/>
+      <c r="AB88" s="38"/>
+      <c r="AD88" s="38"/>
+      <c r="AE88"/>
+      <c r="AF88" s="41"/>
+      <c r="AG88" s="21"/>
+      <c r="AM88" s="38"/>
+      <c r="AO88" s="38"/>
+      <c r="AQ88" s="38"/>
+      <c r="AR88"/>
+      <c r="AS88" s="41"/>
+      <c r="AT88" s="21"/>
+      <c r="AZ88" s="38"/>
+      <c r="BB88" s="38"/>
+      <c r="BD88" s="38"/>
+      <c r="BE88"/>
+      <c r="BF88" s="41"/>
+      <c r="BM88" s="38"/>
+      <c r="BO88" s="38"/>
+      <c r="BQ88" s="38"/>
+      <c r="BR88"/>
+      <c r="BS88" s="38"/>
+    </row>
+    <row r="89" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M89" s="38"/>
+      <c r="O89" s="38"/>
+      <c r="Q89" s="38"/>
+      <c r="R89"/>
+      <c r="S89" s="41"/>
+      <c r="Z89" s="38"/>
+      <c r="AB89" s="38"/>
+      <c r="AD89" s="38"/>
+      <c r="AE89"/>
+      <c r="AF89" s="41"/>
+      <c r="AG89" s="21"/>
+      <c r="AM89" s="38"/>
+      <c r="AO89" s="38"/>
+      <c r="AQ89" s="38"/>
+      <c r="AR89"/>
+      <c r="AS89" s="41"/>
+      <c r="AT89" s="21"/>
+      <c r="AZ89" s="38"/>
+      <c r="BB89" s="38"/>
+      <c r="BD89" s="38"/>
+      <c r="BE89"/>
+      <c r="BF89" s="41"/>
+      <c r="BM89" s="38"/>
+      <c r="BO89" s="38"/>
+      <c r="BQ89" s="38"/>
+      <c r="BR89"/>
+      <c r="BS89" s="38"/>
+    </row>
+    <row r="90" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M90" s="38"/>
+      <c r="O90" s="38"/>
+      <c r="Q90" s="38"/>
+      <c r="R90"/>
+      <c r="S90" s="41"/>
+      <c r="Z90" s="38"/>
+      <c r="AB90" s="38"/>
+      <c r="AD90" s="38"/>
+      <c r="AE90"/>
+      <c r="AF90" s="41"/>
+      <c r="AG90" s="21"/>
+      <c r="AM90" s="38"/>
+      <c r="AO90" s="38"/>
+      <c r="AQ90" s="38"/>
+      <c r="AR90"/>
+      <c r="AS90" s="41"/>
+      <c r="AT90" s="21"/>
+      <c r="AZ90" s="38"/>
+      <c r="BB90" s="38"/>
+      <c r="BD90" s="38"/>
+      <c r="BE90"/>
+      <c r="BF90" s="41"/>
+      <c r="BM90" s="38"/>
+      <c r="BO90" s="38"/>
+      <c r="BQ90" s="38"/>
+      <c r="BR90"/>
+      <c r="BS90" s="38"/>
+    </row>
+    <row r="91" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M91" s="38"/>
+      <c r="O91" s="38"/>
+      <c r="Q91" s="38"/>
+      <c r="R91"/>
+      <c r="S91" s="41"/>
+      <c r="Z91" s="38"/>
+      <c r="AB91" s="38"/>
+      <c r="AD91" s="38"/>
+      <c r="AE91"/>
+      <c r="AF91" s="41"/>
+      <c r="AG91" s="21"/>
+      <c r="AM91" s="38"/>
+      <c r="AO91" s="38"/>
+      <c r="AQ91" s="38"/>
+      <c r="AR91"/>
+      <c r="AS91" s="41"/>
+      <c r="AT91" s="21"/>
+      <c r="AZ91" s="38"/>
+      <c r="BB91" s="38"/>
+      <c r="BD91" s="38"/>
+      <c r="BE91"/>
+      <c r="BF91" s="41"/>
+      <c r="BM91" s="38"/>
+      <c r="BO91" s="38"/>
+      <c r="BQ91" s="38"/>
+      <c r="BR91"/>
+      <c r="BS91" s="38"/>
+    </row>
+    <row r="92" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M92" s="38"/>
+      <c r="O92" s="38"/>
+      <c r="Q92" s="38"/>
+      <c r="R92"/>
+      <c r="S92" s="41"/>
+      <c r="Z92" s="38"/>
+      <c r="AB92" s="38"/>
+      <c r="AD92" s="38"/>
+      <c r="AE92"/>
+      <c r="AF92" s="41"/>
+      <c r="AG92" s="21"/>
+      <c r="AM92" s="38"/>
+      <c r="AO92" s="38"/>
+      <c r="AQ92" s="38"/>
+      <c r="AR92"/>
+      <c r="AS92" s="41"/>
+      <c r="AT92" s="21"/>
+      <c r="AZ92" s="38"/>
+      <c r="BB92" s="38"/>
+      <c r="BD92" s="38"/>
+      <c r="BE92"/>
+      <c r="BF92" s="41"/>
+      <c r="BM92" s="38"/>
+      <c r="BO92" s="38"/>
+      <c r="BQ92" s="38"/>
+      <c r="BR92"/>
+      <c r="BS92" s="38"/>
+    </row>
+    <row r="93" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M93" s="38"/>
+      <c r="O93" s="38"/>
+      <c r="Q93" s="38"/>
+      <c r="R93"/>
+      <c r="S93" s="41"/>
+      <c r="Z93" s="38"/>
+      <c r="AB93" s="38"/>
+      <c r="AD93" s="38"/>
+      <c r="AE93"/>
+      <c r="AF93" s="41"/>
+      <c r="AG93" s="21"/>
+      <c r="AM93" s="38"/>
+      <c r="AO93" s="38"/>
+      <c r="AQ93" s="38"/>
+      <c r="AR93"/>
+      <c r="AS93" s="41"/>
+      <c r="AT93" s="21"/>
+      <c r="AZ93" s="38"/>
+      <c r="BB93" s="38"/>
+      <c r="BD93" s="38"/>
+      <c r="BE93"/>
+      <c r="BF93" s="41"/>
+      <c r="BM93" s="38"/>
+      <c r="BO93" s="38"/>
+      <c r="BQ93" s="38"/>
+      <c r="BR93"/>
+      <c r="BS93" s="38"/>
+    </row>
+    <row r="94" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M94" s="38"/>
+      <c r="O94" s="38"/>
+      <c r="Q94" s="38"/>
+      <c r="R94"/>
+      <c r="S94" s="41"/>
+      <c r="Z94" s="38"/>
+      <c r="AB94" s="38"/>
+      <c r="AD94" s="38"/>
+      <c r="AE94"/>
+      <c r="AF94" s="41"/>
+      <c r="AG94" s="21"/>
+      <c r="AM94" s="38"/>
+      <c r="AO94" s="38"/>
+      <c r="AQ94" s="38"/>
+      <c r="AR94"/>
+      <c r="AS94" s="41"/>
+      <c r="AT94" s="21"/>
+      <c r="AZ94" s="38"/>
+      <c r="BB94" s="38"/>
+      <c r="BD94" s="38"/>
+      <c r="BE94"/>
+      <c r="BF94" s="41"/>
+      <c r="BM94" s="38"/>
+      <c r="BO94" s="38"/>
+      <c r="BQ94" s="38"/>
+      <c r="BR94"/>
+      <c r="BS94" s="38"/>
+    </row>
+    <row r="95" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M95" s="38"/>
+      <c r="O95" s="38"/>
+      <c r="Q95" s="38"/>
+      <c r="R95"/>
+      <c r="S95" s="41"/>
+      <c r="Z95" s="38"/>
+      <c r="AB95" s="38"/>
+      <c r="AD95" s="38"/>
+      <c r="AE95"/>
+      <c r="AF95" s="41"/>
+      <c r="AG95" s="21"/>
+      <c r="AM95" s="38"/>
+      <c r="AO95" s="38"/>
+      <c r="AQ95" s="38"/>
+      <c r="AR95"/>
+      <c r="AS95" s="41"/>
+      <c r="AT95" s="21"/>
+      <c r="AZ95" s="38"/>
+      <c r="BB95" s="38"/>
+      <c r="BD95" s="38"/>
+      <c r="BE95"/>
+      <c r="BF95" s="41"/>
+      <c r="BM95" s="38"/>
+      <c r="BO95" s="38"/>
+      <c r="BQ95" s="38"/>
+      <c r="BR95"/>
+      <c r="BS95" s="38"/>
+    </row>
+    <row r="96" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M96" s="38"/>
+      <c r="O96" s="38"/>
+      <c r="Q96" s="38"/>
+      <c r="R96"/>
+      <c r="S96" s="41"/>
+      <c r="Z96" s="38"/>
+      <c r="AB96" s="38"/>
+      <c r="AD96" s="38"/>
+      <c r="AE96"/>
+      <c r="AF96" s="41"/>
+      <c r="AG96" s="21"/>
+      <c r="AM96" s="38"/>
+      <c r="AO96" s="38"/>
+      <c r="AQ96" s="38"/>
+      <c r="AR96"/>
+      <c r="AS96" s="41"/>
+      <c r="AT96" s="21"/>
+      <c r="AZ96" s="38"/>
+      <c r="BB96" s="38"/>
+      <c r="BD96" s="38"/>
+      <c r="BE96"/>
+      <c r="BF96" s="41"/>
+      <c r="BM96" s="38"/>
+      <c r="BO96" s="38"/>
+      <c r="BQ96" s="38"/>
+      <c r="BR96"/>
+      <c r="BS96" s="38"/>
+    </row>
+    <row r="97" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M97" s="38"/>
+      <c r="O97" s="38"/>
+      <c r="Q97" s="38"/>
+      <c r="R97"/>
+      <c r="S97" s="41"/>
+      <c r="Z97" s="38"/>
+      <c r="AB97" s="38"/>
+      <c r="AD97" s="38"/>
+      <c r="AE97"/>
+      <c r="AF97" s="41"/>
+      <c r="AG97" s="21"/>
+      <c r="AM97" s="38"/>
+      <c r="AO97" s="38"/>
+      <c r="AQ97" s="38"/>
+      <c r="AR97"/>
+      <c r="AS97" s="41"/>
+      <c r="AT97" s="21"/>
+      <c r="AZ97" s="38"/>
+      <c r="BB97" s="38"/>
+      <c r="BD97" s="38"/>
+      <c r="BE97"/>
+      <c r="BF97" s="41"/>
+      <c r="BM97" s="38"/>
+      <c r="BO97" s="38"/>
+      <c r="BQ97" s="38"/>
+      <c r="BR97"/>
+      <c r="BS97" s="38"/>
+    </row>
+    <row r="98" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M98" s="38"/>
+      <c r="O98" s="38"/>
+      <c r="Q98" s="38"/>
+      <c r="R98"/>
+      <c r="S98" s="41"/>
+      <c r="Z98" s="38"/>
+      <c r="AB98" s="38"/>
+      <c r="AD98" s="38"/>
+      <c r="AE98"/>
+      <c r="AF98" s="41"/>
+      <c r="AG98" s="21"/>
+      <c r="AM98" s="38"/>
+      <c r="AO98" s="38"/>
+      <c r="AQ98" s="38"/>
+      <c r="AR98"/>
+      <c r="AS98" s="41"/>
+      <c r="AT98" s="21"/>
+      <c r="AZ98" s="38"/>
+      <c r="BB98" s="38"/>
+      <c r="BD98" s="38"/>
+      <c r="BE98"/>
+      <c r="BF98" s="41"/>
+      <c r="BM98" s="38"/>
+      <c r="BO98" s="38"/>
+      <c r="BQ98" s="38"/>
+      <c r="BR98"/>
+      <c r="BS98" s="38"/>
+    </row>
+    <row r="99" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M99" s="38"/>
+      <c r="O99" s="38"/>
+      <c r="Q99" s="38"/>
+      <c r="R99"/>
+      <c r="S99" s="41"/>
+      <c r="Z99" s="38"/>
+      <c r="AB99" s="38"/>
+      <c r="AD99" s="38"/>
+      <c r="AE99"/>
+      <c r="AF99" s="41"/>
+      <c r="AG99" s="21"/>
+      <c r="AM99" s="38"/>
+      <c r="AO99" s="38"/>
+      <c r="AQ99" s="38"/>
+      <c r="AR99"/>
+      <c r="AS99" s="41"/>
+      <c r="AT99" s="21"/>
+      <c r="AZ99" s="38"/>
+      <c r="BB99" s="38"/>
+      <c r="BD99" s="38"/>
+      <c r="BE99"/>
+      <c r="BF99" s="41"/>
+      <c r="BM99" s="38"/>
+      <c r="BO99" s="38"/>
+      <c r="BQ99" s="38"/>
+      <c r="BR99"/>
+      <c r="BS99" s="38"/>
+    </row>
+    <row r="100" spans="13:71" x14ac:dyDescent="0.3">
+      <c r="M100" s="38"/>
+      <c r="O100" s="38"/>
+      <c r="Q100" s="38"/>
+      <c r="R100"/>
+      <c r="S100" s="41"/>
+      <c r="Z100" s="38"/>
+      <c r="AB100" s="38"/>
+      <c r="AD100" s="38"/>
+      <c r="AE100"/>
+      <c r="AF100" s="41"/>
+      <c r="AG100" s="21"/>
+      <c r="AM100" s="38"/>
+      <c r="AO100" s="38"/>
+      <c r="AQ100" s="38"/>
+      <c r="AR100"/>
+      <c r="AS100" s="41"/>
+      <c r="AT100" s="21"/>
+      <c r="AZ100" s="38"/>
+      <c r="BB100" s="38"/>
+      <c r="BD100" s="38"/>
+      <c r="BE100"/>
+      <c r="BF100" s="41"/>
+      <c r="BM100" s="38"/>
+      <c r="BO100" s="38"/>
+      <c r="BQ100" s="38"/>
+      <c r="BR100"/>
+      <c r="BS100" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="S1:AE1"/>
     <mergeCell ref="AF1:AR1"/>
     <mergeCell ref="AS1:BE1"/>
+    <mergeCell ref="BF1:BR1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2301,23 +5950,23 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="select" xr:uid="{A3F18C05-5A22-4FAE-B7B1-867FB364451F}">
-          <x14:formula1>
-            <xm:f>options!$G$2:$G$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>L1048553 BA3 L3 N3 Y3 AA3 AL3 AN3 AY3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="select" xr:uid="{52B7E54D-8249-4ACA-86FB-99C95F3C1C28}">
-          <x14:formula1>
-            <xm:f>options!$I$2:$I$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>P3 R3 AC3 AE3 AP3 AR3 BC3 BE3</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select" xr:uid="{1AE8C625-C844-47E0-93DE-53765917A448}">
           <x14:formula1>
             <xm:f>options!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>AY5</xm:sqref>
+          <xm:sqref>AZ100</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="soil moisture" prompt="indicate if measurement is gravimetric (% g/g) or volumetric (% V/V)" xr:uid="{95BC60E9-AF61-486E-9DBD-C211EE4FBBF0}">
+          <x14:formula1>
+            <xm:f>options!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>M3:M99 O3:O99 Z3:Z99 BO3:BO99 AM3:AM99 AO3:AO99 AZ3:AZ99 BB3:BB99 BM3:BM99 AB3:AB99</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="measurement units" prompt="select mg N/ha. or kg N/ha." xr:uid="{7A34E804-1F1D-4C2A-861F-919BB0C44744}">
+          <x14:formula1>
+            <xm:f>options!$I$2:$I$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q3:Q100 S3:S100 AD3:AD100 AF3:AF100 AQ3:AQ100 AS3:AS100 BD3:BD100 BF3:BF100 BQ3:BQ100 BS3:BT3 BS4:BS100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2330,33 +5979,463 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="18" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D2" s="25"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="21"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" s="40"/>
+      <c r="D3" s="21"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C4" s="40"/>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C5" s="40"/>
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C6" s="40"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C7" s="40"/>
+      <c r="D7" s="21"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C8" s="40"/>
+      <c r="D8" s="21"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C9" s="40"/>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C10" s="40"/>
+      <c r="D10" s="21"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C11" s="40"/>
+      <c r="D11" s="21"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C12" s="40"/>
+      <c r="D12" s="21"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C13" s="40"/>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C14" s="40"/>
+      <c r="D14" s="21"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C15" s="40"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C16" s="40"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C17" s="40"/>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C18" s="40"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C19" s="40"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C20" s="40"/>
+      <c r="D20" s="21"/>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C21" s="40"/>
+      <c r="D21" s="21"/>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C22" s="40"/>
+      <c r="D22" s="21"/>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C23" s="40"/>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C24" s="40"/>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C25" s="40"/>
+      <c r="D25" s="21"/>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C26" s="40"/>
+      <c r="D26" s="21"/>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C27" s="40"/>
+      <c r="D27" s="21"/>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C28" s="40"/>
+      <c r="D28" s="21"/>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C29" s="40"/>
+      <c r="D29" s="21"/>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C30" s="40"/>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C31" s="40"/>
+      <c r="D31" s="21"/>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C32" s="40"/>
+      <c r="D32" s="21"/>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C33" s="40"/>
+      <c r="D33" s="21"/>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C34" s="40"/>
+      <c r="D34" s="21"/>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C35" s="40"/>
+      <c r="D35" s="21"/>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C36" s="40"/>
+      <c r="D36" s="21"/>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C37" s="40"/>
+      <c r="D37" s="21"/>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C38" s="40"/>
+      <c r="D38" s="21"/>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C39" s="40"/>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C40" s="40"/>
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C41" s="40"/>
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C42" s="40"/>
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C43" s="40"/>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C44" s="40"/>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C45" s="40"/>
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C46" s="40"/>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C47" s="40"/>
+      <c r="D47" s="21"/>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C48" s="40"/>
+      <c r="D48" s="21"/>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49" s="40"/>
+      <c r="D49" s="21"/>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C50" s="40"/>
+      <c r="D50" s="21"/>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C51" s="40"/>
+      <c r="D51" s="21"/>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C52" s="40"/>
+      <c r="D52" s="21"/>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C53" s="40"/>
+      <c r="D53" s="21"/>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C54" s="40"/>
+      <c r="D54" s="21"/>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C55" s="40"/>
+      <c r="D55" s="21"/>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C56" s="40"/>
+      <c r="D56" s="21"/>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C57" s="40"/>
+      <c r="D57" s="21"/>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C58" s="40"/>
+      <c r="D58" s="21"/>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C59" s="40"/>
+      <c r="D59" s="21"/>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C60" s="40"/>
+      <c r="D60" s="21"/>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C61" s="40"/>
+      <c r="D61" s="21"/>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C62" s="40"/>
+      <c r="D62" s="21"/>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C63" s="40"/>
+      <c r="D63" s="21"/>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C64" s="40"/>
+      <c r="D64" s="21"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C65" s="40"/>
+      <c r="D65" s="21"/>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C66" s="40"/>
+      <c r="D66" s="21"/>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C67" s="40"/>
+      <c r="D67" s="21"/>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C68" s="40"/>
+      <c r="D68" s="21"/>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C69" s="40"/>
+      <c r="D69" s="21"/>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C70" s="40"/>
+      <c r="D70" s="21"/>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C71" s="40"/>
+      <c r="D71" s="21"/>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C72" s="40"/>
+      <c r="D72" s="21"/>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C73" s="40"/>
+      <c r="D73" s="21"/>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C74" s="40"/>
+      <c r="D74" s="21"/>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C75" s="40"/>
+      <c r="D75" s="21"/>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C76" s="40"/>
+      <c r="D76" s="21"/>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C77" s="40"/>
+      <c r="D77" s="21"/>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C78" s="40"/>
+      <c r="D78" s="21"/>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C79" s="40"/>
+      <c r="D79" s="21"/>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C80" s="40"/>
+      <c r="D80" s="21"/>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C81" s="40"/>
+      <c r="D81" s="21"/>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C82" s="40"/>
+      <c r="D82" s="21"/>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C83" s="40"/>
+      <c r="D83" s="21"/>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C84" s="40"/>
+      <c r="D84" s="21"/>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C85" s="40"/>
+      <c r="D85" s="21"/>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C86" s="40"/>
+      <c r="D86" s="21"/>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C87" s="40"/>
+      <c r="D87" s="21"/>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C88" s="40"/>
+      <c r="D88" s="21"/>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C89" s="40"/>
+      <c r="D89" s="21"/>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C90" s="40"/>
+      <c r="D90" s="21"/>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C91" s="40"/>
+      <c r="D91" s="21"/>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C92" s="40"/>
+      <c r="D92" s="21"/>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C93" s="40"/>
+      <c r="D93" s="21"/>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C94" s="40"/>
+      <c r="D94" s="21"/>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C95" s="40"/>
+      <c r="D95" s="21"/>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C96" s="40"/>
+      <c r="D96" s="21"/>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C97" s="40"/>
+      <c r="D97" s="21"/>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C98" s="40"/>
+      <c r="D98" s="21"/>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C99" s="40"/>
+      <c r="D99" s="21"/>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C100" s="40"/>
+      <c r="D100" s="21"/>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C101" s="40"/>
+      <c r="D101" s="21"/>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C102" s="40"/>
+      <c r="D102" s="21"/>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C103" s="40"/>
+      <c r="D103" s="21"/>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C104" s="40"/>
+      <c r="D104" s="21"/>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C105" s="40"/>
+      <c r="D105" s="21"/>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C106" s="40"/>
+      <c r="D106" s="21"/>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C107" s="40"/>
+      <c r="D107" s="21"/>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C108" s="40"/>
+      <c r="D108" s="21"/>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C109" s="40"/>
+      <c r="D109" s="21"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2364,11 +6443,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select" xr:uid="{79FA6A2E-55D0-4BA5-8479-2BFA6A650D99}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3154B2D3-9007-4AB1-87EE-004F853B8D1A}">
           <x14:formula1>
             <xm:f>options!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>C2</xm:sqref>
+          <xm:sqref>C2:C109</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2381,42 +6460,42 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="23.44140625" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" customWidth="1"/>
-    <col min="7" max="8" width="18.21875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="18.21875" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="5"/>
-      <c r="D1" s="33" t="s">
+      <c r="C1"/>
+      <c r="D1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="35" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="61"/>
+      <c r="I1" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="36"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2428,51 +6507,539 @@
       <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="49" t="s">
         <v>85</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="50" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J3"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D4" s="39"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D5" s="39"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D6" s="39"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D7" s="39"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D8" s="39"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D9" s="39"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D10" s="39"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D11" s="39"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D12" s="39"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D13" s="39"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D14" s="39"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D15" s="39"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D16" s="39"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D17" s="39"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D18" s="39"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D19" s="39"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D20" s="39"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="39"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="39"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D23" s="39"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D24" s="39"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D25" s="39"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D26" s="39"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+    </row>
+    <row r="27" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D27" s="39"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D28" s="39"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="39"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+    </row>
+    <row r="30" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D30" s="39"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+    </row>
+    <row r="31" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D31" s="39"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+    </row>
+    <row r="32" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D32" s="39"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+    </row>
+    <row r="33" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D33" s="39"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+    </row>
+    <row r="34" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D34" s="39"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D35" s="39"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+    </row>
+    <row r="36" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D36" s="39"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+    </row>
+    <row r="37" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D37" s="39"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+    </row>
+    <row r="38" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D38" s="39"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+    </row>
+    <row r="39" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D39" s="39"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+    </row>
+    <row r="40" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D40" s="39"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+    </row>
+    <row r="41" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D41" s="39"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+    </row>
+    <row r="42" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D42" s="39"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+    </row>
+    <row r="43" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D43" s="39"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+    </row>
+    <row r="44" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D44" s="39"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+    </row>
+    <row r="45" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D45" s="39"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+    </row>
+    <row r="46" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D46" s="39"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+    </row>
+    <row r="47" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D47" s="39"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+    </row>
+    <row r="48" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D48" s="39"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
+    </row>
+    <row r="49" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D49" s="39"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+    </row>
+    <row r="50" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D50" s="39"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+    </row>
+    <row r="51" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D51" s="39"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+    </row>
+    <row r="52" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D52" s="39"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+    </row>
+    <row r="53" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D53" s="39"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+    </row>
+    <row r="54" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D54" s="39"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+    </row>
+    <row r="55" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D55" s="39"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+    </row>
+    <row r="56" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D56" s="39"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+    </row>
+    <row r="57" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D57" s="39"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+    </row>
+    <row r="58" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D58" s="39"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+    </row>
+    <row r="59" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D59" s="39"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+    </row>
+    <row r="60" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D60" s="39"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+    </row>
+    <row r="61" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D61" s="39"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+    </row>
+    <row r="62" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D62" s="39"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+    </row>
+    <row r="63" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D63" s="39"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+    </row>
+    <row r="64" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D64" s="39"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+    </row>
+    <row r="65" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D65" s="39"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+    </row>
+    <row r="66" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D66" s="39"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+    </row>
+    <row r="67" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D67" s="39"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+    </row>
+    <row r="68" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D68" s="39"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+    </row>
+    <row r="69" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D69" s="39"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+    </row>
+    <row r="70" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D70" s="39"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+    </row>
+    <row r="71" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D71" s="39"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+    </row>
+    <row r="72" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D72" s="39"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+    </row>
+    <row r="73" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D73" s="39"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+    </row>
+    <row r="74" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D74" s="39"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+    </row>
+    <row r="75" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D75" s="39"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+    </row>
+    <row r="76" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D76" s="39"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+    </row>
+    <row r="77" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D77" s="39"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+    </row>
+    <row r="78" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D78" s="39"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+    </row>
+    <row r="79" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D79" s="39"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+    </row>
+    <row r="80" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D80" s="39"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+    </row>
+    <row r="81" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D81" s="39"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+    </row>
+    <row r="82" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D82" s="39"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+    </row>
+    <row r="83" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D83" s="39"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+    </row>
+    <row r="84" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D84" s="39"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+    </row>
+    <row r="85" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D85" s="39"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38"/>
+    </row>
+    <row r="86" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D86" s="39"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+    </row>
+    <row r="87" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D87" s="39"/>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38"/>
+    </row>
+    <row r="88" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D88" s="39"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
+    </row>
+    <row r="89" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D89" s="39"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38"/>
+    </row>
+    <row r="90" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D90" s="39"/>
+      <c r="E90" s="38"/>
+      <c r="F90" s="38"/>
+    </row>
+    <row r="91" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D91" s="39"/>
+      <c r="E91" s="38"/>
+      <c r="F91" s="38"/>
+    </row>
+    <row r="92" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D92" s="39"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+    </row>
+    <row r="93" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D93" s="39"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
+    </row>
+    <row r="94" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D94" s="39"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+    </row>
+    <row r="95" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D95" s="39"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38"/>
+    </row>
+    <row r="96" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D96" s="39"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="38"/>
+    </row>
+    <row r="97" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D97" s="39"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
+    </row>
+    <row r="98" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D98" s="39"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
+    </row>
+    <row r="99" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D99" s="39"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+    </row>
+    <row r="100" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D100" s="39"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{858421A4-8C59-4280-B377-5E030D8CF720}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="602" yWindow="502" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="select management file" xr:uid="{858421A4-8C59-4280-B377-5E030D8CF720}">
           <x14:formula1>
             <xm:f>management!$A$3:$A$525</xm:f>
           </x14:formula1>
-          <xm:sqref>D3</xm:sqref>
+          <xm:sqref>D3:D100</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6E91F0E-AB66-4F4A-839B-CBBD65E80C13}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="select soil profile" xr:uid="{D6E91F0E-AB66-4F4A-839B-CBBD65E80C13}">
           <x14:formula1>
-            <xm:f>soils!$A$3:$A$525</xm:f>
+            <xm:f>soils!$A$3:$A$620</xm:f>
           </x14:formula1>
-          <xm:sqref>E3</xm:sqref>
+          <xm:sqref>E3:E100</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7FFA221B-67EF-4381-AB06-C175A80C81B2}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="select weather station" xr:uid="{7FFA221B-67EF-4381-AB06-C175A80C81B2}">
           <x14:formula1>
-            <xm:f>stations!$A$2:$A$525</xm:f>
+            <xm:f>stations!$A$2:$A$632</xm:f>
           </x14:formula1>
-          <xm:sqref>F3</xm:sqref>
+          <xm:sqref>F3:F100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2481,6 +7048,146 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB6638A-DDAC-4943-98A1-E4C6A7719FC0}">
+  <sheetPr>
+    <tabColor rgb="FFCCCCFF"/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="6"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="41"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="41"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="41"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="41"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="41"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="41"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="41"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="41"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="41"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="41"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="41"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="41"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="41"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="41"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="41"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="41"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="41"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="41"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="41"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="41"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="41"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="41"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="41"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="41"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="41"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="41"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="41"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="41"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="41"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="select usm" xr:uid="{6920C176-8703-46A9-838A-D72537307E00}">
+          <x14:formula1>
+            <xm:f>usms!$A$3:$A$325</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A30</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA73EF4-F459-4FB8-999B-97CF29F368C2}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2503,10 +7210,10 @@
         <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2520,10 +7227,10 @@
         <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2537,10 +7244,10 @@
         <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">

--- a/files/Templates/collected_data.xlsx
+++ b/files/Templates/collected_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marpo\Documents\Research\STICS\Code\mkSTICSfiles\files\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marpo\Documents\Research\STICS\Code\mkSTICSfiles\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8435BD-6E33-4294-89A4-E4A9A779B45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424D330F-59F3-4D69-84F8-7B0E19D330F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="30936" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="management" sheetId="8" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="stations" sheetId="6" r:id="rId3"/>
     <sheet name="usms" sheetId="1" r:id="rId4"/>
     <sheet name="observations" sheetId="9" r:id="rId5"/>
-    <sheet name="options" sheetId="4" state="hidden" r:id="rId6"/>
+    <sheet name="options" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Fertilizer_Application">Table3[Fertilizer_Application]</definedName>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="178">
   <si>
     <t>usm_name</t>
   </si>
@@ -421,9 +421,6 @@
     <t>amount_15</t>
   </si>
   <si>
-    <t>irrigation_date_16</t>
-  </si>
-  <si>
     <t>Irrigation</t>
   </si>
   <si>
@@ -557,6 +554,36 @@
   </si>
   <si>
     <t>albedo</t>
+  </si>
+  <si>
+    <t>harvest_end</t>
+  </si>
+  <si>
+    <t>harvest_date2</t>
+  </si>
+  <si>
+    <t>automatic_irr_depth</t>
+  </si>
+  <si>
+    <t>harvest</t>
+  </si>
+  <si>
+    <t>irrigation_type</t>
+  </si>
+  <si>
+    <t>irr_efficiency</t>
+  </si>
+  <si>
+    <t>Irrigation Location</t>
+  </si>
+  <si>
+    <t>1 = above the foliage</t>
+  </si>
+  <si>
+    <t>2 = below the foliage above the soil</t>
+  </si>
+  <si>
+    <t>3 = in the soil</t>
   </si>
 </sst>
 </file>
@@ -601,7 +628,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,6 +785,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="gray0625">
+        <fgColor theme="0" tint="-0.14993743705557422"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -908,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -962,6 +995,10 @@
     <xf numFmtId="0" fontId="3" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -989,122 +1026,30 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="55">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -1166,76 +1111,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -1565,6 +1440,171 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1591,24 +1631,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AT100" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7">
-  <autoFilter ref="A2:AT100" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
-  <tableColumns count="46">
-    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AX100" totalsRowShown="0" headerRowDxfId="48" headerRowBorderDxfId="47" tableBorderDxfId="46">
+  <autoFilter ref="A2:AX100" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
+  <tableColumns count="50">
+    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="44"/>
     <tableColumn id="3" xr3:uid="{416116E5-319A-4096-B7E5-AF8ADEF0E80A}" name="tillage_date"/>
-    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="43"/>
     <tableColumn id="5" xr3:uid="{A768ED69-1CCB-4A41-99C1-D5042177408B}" name="planting_date"/>
     <tableColumn id="6" xr3:uid="{5517C570-4D1C-46EC-9FB0-4FEA929440E1}" name="planting_depth"/>
-    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="42"/>
     <tableColumn id="8" xr3:uid="{7DEB259C-DAE3-4A1E-B476-951FEF30ABD2}" name="emergence"/>
     <tableColumn id="9" xr3:uid="{8590CC43-CF1F-45A9-A612-CE3749B53C84}" name="flowering"/>
-    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="41"/>
     <tableColumn id="11" xr3:uid="{1651DE3B-149A-4121-AFB0-BA33E8308050}" name="application_date"/>
     <tableColumn id="12" xr3:uid="{358B23A5-F859-4B79-9182-F98F3D69F461}" name="kg_N_per_ha"/>
     <tableColumn id="13" xr3:uid="{FEB67719-45D9-4389-A438-548C552EBED6}" name="fert_type"/>
     <tableColumn id="14" xr3:uid="{B9B3005C-6E63-4AA3-BE8E-646D9659B76F}" name="fert_location"/>
-    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="40"/>
+    <tableColumn id="49" xr3:uid="{1DACF6E4-1D01-4D98-B61F-06AED8D28283}" name="irrigation_type"/>
+    <tableColumn id="48" xr3:uid="{E053F1CC-2741-44D0-BCB6-E2638B921A91}" name="irr_efficiency"/>
     <tableColumn id="16" xr3:uid="{AA12C7D8-D645-4337-B05C-CB5F5C197AE4}" name="irrigation_date_1"/>
     <tableColumn id="17" xr3:uid="{017BC113-D478-4E04-AEE6-020CA6B48738}" name="amount_1"/>
     <tableColumn id="18" xr3:uid="{498ED556-89DC-49A5-A6C1-DF741DBED2EF}" name="irrigation_date_2"/>
@@ -1639,7 +1681,9 @@
     <tableColumn id="43" xr3:uid="{0A0B6CAB-9EC9-4492-A667-1846AE54A020}" name="amount_14"/>
     <tableColumn id="44" xr3:uid="{7DD1FA19-1C12-4443-9EB3-267851A488BA}" name="irrigation_date_15"/>
     <tableColumn id="45" xr3:uid="{A69E1720-4BA7-4736-9E85-A0E33013B090}" name="amount_15"/>
-    <tableColumn id="46" xr3:uid="{A0DFD622-ADA5-48E2-B689-A17242FFBEEA}" name="irrigation_date_16"/>
+    <tableColumn id="51" xr3:uid="{D644A008-911D-42DE-B5AE-3D97E8D9CBE3}" name="automatic_irr_depth"/>
+    <tableColumn id="47" xr3:uid="{8142D301-45D6-476E-91F5-4C775D8382CE}" name="harvest_date2"/>
+    <tableColumn id="50" xr3:uid="{A3119A2B-1FF4-4688-A8C7-EA84F5130A56}" name="harvest_end"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1655,11 +1699,21 @@
 </table>
 </file>
 
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{EC7F3CD2-B7DD-4AB9-A1D1-61C6B8E31CF2}" name="Table11" displayName="Table11" ref="K1:K4" totalsRowShown="0">
+  <autoFilter ref="K1:K4" xr:uid="{EC7F3CD2-B7DD-4AB9-A1D1-61C6B8E31CF2}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{684BC5C4-FC4C-4A03-9843-BEAD87C7E594}" name="Irrigation Location"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:BS100" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:BS100" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="A2:BS100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
   <tableColumns count="71">
-    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="36"/>
     <tableColumn id="2" xr3:uid="{72D785FE-A1AF-4E08-AB14-39FAD15DB9BD}" name="thickness_1"/>
     <tableColumn id="3" xr3:uid="{1838D7E8-2B3C-471C-9A0B-D70D91F18417}" name="pH"/>
     <tableColumn id="71" xr3:uid="{931F79EB-F524-439C-8A88-ED674075FA7F}" name="albedo"/>
@@ -1671,110 +1725,110 @@
     <tableColumn id="40" xr3:uid="{EC836542-6DD7-49C9-82D9-B724BCE18341}" name="SON_1"/>
     <tableColumn id="41" xr3:uid="{F7750E58-5B0E-4494-87AF-B025671824DE}" name="CN_ratio"/>
     <tableColumn id="8" xr3:uid="{0592115C-328E-42C4-B9CB-D43026D4FC27}" name="FC_1"/>
-    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="50"/>
+    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="35"/>
     <tableColumn id="9" xr3:uid="{C1383A59-387E-4667-852A-B0CF467088F3}" name="WP_1"/>
-    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="49"/>
+    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="34"/>
     <tableColumn id="10" xr3:uid="{34D0D911-5DB4-457F-88A7-76A42B57EE1A}" name="initial_NO3_1"/>
-    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="48"/>
+    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="33"/>
     <tableColumn id="53" xr3:uid="{CEF78893-60AA-4A20-A771-E76562B8EBC1}" name="initial_NH4_1"/>
-    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="47"/>
+    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="32"/>
     <tableColumn id="12" xr3:uid="{FD043EB5-2678-4920-8D76-EBE8316E27AA}" name="thickness_2"/>
     <tableColumn id="13" xr3:uid="{F124AE04-B447-4F21-A0E8-7B26199C0F49}" name="%_sand_2"/>
     <tableColumn id="14" xr3:uid="{F119498A-3A35-40E3-A753-7CF13D724118}" name="%_clay_2"/>
     <tableColumn id="15" xr3:uid="{AE51522F-6903-42D4-88CE-A95BCE8C77EF}" name="BD_2"/>
     <tableColumn id="16" xr3:uid="{12076489-6AD7-4297-A729-20EF93AEE58D}" name="SOC_2"/>
     <tableColumn id="17" xr3:uid="{D6D5EFD4-69CC-4AF2-8C6B-0B430468C4C2}" name="FC_2"/>
-    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="46"/>
+    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="31"/>
     <tableColumn id="18" xr3:uid="{BBF6A61D-2092-4DF7-8C38-9024164291AE}" name="WP_2"/>
-    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="45"/>
+    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="30"/>
     <tableColumn id="19" xr3:uid="{BB4B796C-CA3E-424C-87B0-4BF33581B61B}" name="initial_NO3_2"/>
-    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="44"/>
+    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="29"/>
     <tableColumn id="55" xr3:uid="{333E59C3-3A13-4C92-9169-AC90D5E5D3EB}" name="initial_NH4_2"/>
-    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="43"/>
-    <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3" dataDxfId="42"/>
+    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="28"/>
+    <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3" dataDxfId="27"/>
     <tableColumn id="22" xr3:uid="{6C917DE4-8D95-496E-A6F1-EAB7450774EE}" name="%_sand_3"/>
     <tableColumn id="23" xr3:uid="{90DE7FE2-3A23-4294-8BD0-2D321FF71179}" name="%_clay_3"/>
     <tableColumn id="24" xr3:uid="{C874CBBB-CB06-4239-AE9B-72564A3EDC14}" name="BD_3"/>
     <tableColumn id="25" xr3:uid="{49CED3FB-E83C-4973-A99D-DAC6B3AFC7B1}" name="SOC_3"/>
     <tableColumn id="26" xr3:uid="{63FB3901-EBED-4379-9E9C-83064A8ADD01}" name="FC_3"/>
-    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="41"/>
+    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="26"/>
     <tableColumn id="27" xr3:uid="{6EEACF0E-3934-49DF-9991-42C2DB718BE0}" name="WP_3"/>
-    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="40"/>
+    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="25"/>
     <tableColumn id="28" xr3:uid="{7AAE3F1E-C60E-4E11-A023-F09548D5AA39}" name="initial_NO3_3"/>
-    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="39"/>
+    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="24"/>
     <tableColumn id="57" xr3:uid="{1D0A3587-38DB-4073-B5D4-36DA82425955}" name="initial_NH4_3"/>
-    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="38"/>
-    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="37"/>
+    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="23"/>
+    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="22"/>
     <tableColumn id="31" xr3:uid="{4C1178FA-055B-4F19-A181-638D37A24EB6}" name="%_sand_4"/>
     <tableColumn id="32" xr3:uid="{7BBFA3FD-BBE5-4B68-A551-EFDEA7062540}" name="%_clay_4"/>
     <tableColumn id="33" xr3:uid="{D0607A27-FB9E-4DA9-A7F3-7A932B2608A4}" name="BD_4"/>
     <tableColumn id="34" xr3:uid="{BD46131F-AB56-411A-8742-B77FBBE1967B}" name="SOC_4"/>
     <tableColumn id="35" xr3:uid="{EC2EEDB8-3CC6-4DEE-9309-DBA3B11A2D16}" name="FC_4"/>
-    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="36"/>
-    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="35"/>
-    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="34"/>
-    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="33"/>
-    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="32"/>
-    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="31"/>
-    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="30"/>
+    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="21"/>
+    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="20"/>
+    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="19"/>
+    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="18"/>
+    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="17"/>
+    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="16"/>
+    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="15"/>
     <tableColumn id="46" xr3:uid="{5545ADBB-3E57-4FCE-9979-330500D810A6}" name="thickness_5"/>
     <tableColumn id="49" xr3:uid="{28F4610E-A232-42D7-866E-B72AB5FC38D8}" name="%_sand_5"/>
     <tableColumn id="60" xr3:uid="{9557F7B0-0944-4CA4-8B86-630B4073480C}" name="%_clay_5"/>
     <tableColumn id="61" xr3:uid="{6977D0A0-E571-46FB-8186-DF22D992C4B6}" name="BD_5"/>
     <tableColumn id="62" xr3:uid="{762BF513-B3A9-4714-B788-A74D32CD414B}" name="SOC_5"/>
     <tableColumn id="63" xr3:uid="{F840DA58-F957-445A-8704-4823DC13AEC7}" name="FC_5"/>
-    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="29"/>
+    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="14"/>
     <tableColumn id="65" xr3:uid="{73133DDD-77CC-4B8F-AF63-0B5537B95DE3}" name="WP_5"/>
-    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="28"/>
+    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="13"/>
     <tableColumn id="67" xr3:uid="{AF697735-FE14-47A1-8029-532D47D2E5C7}" name="initial_NO3_5"/>
-    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="27"/>
-    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="26"/>
-    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="25"/>
+    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="12"/>
+    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="11"/>
+    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:D109" totalsRowShown="0" headerRowBorderDxfId="24" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:D109" totalsRowShown="0" headerRowBorderDxfId="54" tableBorderDxfId="53">
   <autoFilter ref="A1:D109" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:J100" totalsRowShown="0" headerRowBorderDxfId="18" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:J100" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A2:J100" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{C58B90D4-B75A-409B-9D58-E09932ABF65C}" name="simulation_start"/>
-    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{C4CB74A7-2660-4D67-9D08-D7802D112D6D}" name="soil_profile_name"/>
     <tableColumn id="6" xr3:uid="{EE8564A9-D685-42B6-914D-B5F77F840B11}" name="weather_station_name"/>
     <tableColumn id="7" xr3:uid="{DF70C6E4-2795-4D3D-B86B-8B48BE8FB3E1}" name="plant_file"/>
-    <tableColumn id="8" xr3:uid="{B3D6750F-E334-4A3F-A048-BA40F1D2EC0C}" name="cultivar_code" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{B3D6750F-E334-4A3F-A048-BA40F1D2EC0C}" name="cultivar_code" dataDxfId="4"/>
     <tableColumn id="9" xr3:uid="{BDB57316-D9C6-4EE3-821F-F5561E0078D9}" name="first_year"/>
-    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="2">
   <autoFilter ref="A1:F30" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{A5156817-2D3F-4E14-AC57-75BA66E12293}" name="year"/>
     <tableColumn id="3" xr3:uid="{173E3383-07EB-425D-884F-01E4ECFF4626}" name="month"/>
-    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{B9B2B184-EF64-48EF-B50B-8E24249DFDCC}" name="variable 1"/>
     <tableColumn id="7" xr3:uid="{ED0F5D28-DB43-4C9B-ADB2-1706AC6D61F9}" name="variable 2"/>
   </tableColumns>
@@ -2088,7 +2142,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AT100"/>
+  <dimension ref="A1:AX100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="5" customWidth="1"/>
@@ -2139,63 +2193,67 @@
     <col min="46" max="46" width="18.21875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="C1" s="51" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="C1" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52" t="s">
+      <c r="D1" s="55"/>
+      <c r="E1" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="54" t="s">
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="53" t="s">
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="55"/>
-      <c r="AF1" s="55"/>
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="55"/>
-      <c r="AR1" s="55"/>
-      <c r="AS1" s="55"/>
-      <c r="AT1" s="55"/>
-    </row>
-    <row r="2" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
+      <c r="X1" s="69"/>
+      <c r="Y1" s="69"/>
+      <c r="Z1" s="69"/>
+      <c r="AA1" s="69"/>
+      <c r="AB1" s="69"/>
+      <c r="AC1" s="69"/>
+      <c r="AD1" s="69"/>
+      <c r="AE1" s="69"/>
+      <c r="AF1" s="69"/>
+      <c r="AG1" s="69"/>
+      <c r="AH1" s="69"/>
+      <c r="AI1" s="69"/>
+      <c r="AJ1" s="69"/>
+      <c r="AK1" s="69"/>
+      <c r="AL1" s="69"/>
+      <c r="AM1" s="69"/>
+      <c r="AN1" s="69"/>
+      <c r="AO1" s="69"/>
+      <c r="AP1" s="69"/>
+      <c r="AQ1" s="69"/>
+      <c r="AR1" s="69"/>
+      <c r="AS1" s="69"/>
+      <c r="AT1" s="69"/>
+      <c r="AU1" s="72"/>
+      <c r="AW1" s="70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>52</v>
       </c>
@@ -2242,500 +2300,901 @@
         <v>62</v>
       </c>
       <c r="P2" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="R2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="AA2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AB2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AD2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AE2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AF2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AG2" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AH2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="AG2" s="11" t="s">
+      <c r="AI2" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="AH2" s="11" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AK2" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="AJ2" s="11" t="s">
+      <c r="AL2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AM2" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="AL2" s="11" t="s">
+      <c r="AN2" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="AM2" s="11" t="s">
+      <c r="AO2" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AP2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="AO2" s="11" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="AP2" s="11" t="s">
+      <c r="AR2" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="AQ2" s="11" t="s">
+      <c r="AS2" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AT2" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="AS2" s="11" t="s">
+      <c r="AU2" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="AT2" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="E3" s="67"/>
+      <c r="AV2" s="71" t="s">
+        <v>170</v>
+      </c>
+      <c r="AW2" s="73" t="s">
+        <v>169</v>
+      </c>
+      <c r="AX2" s="73" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="E3" s="54"/>
       <c r="M3" s="38"/>
       <c r="N3" s="38"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="68"/>
       <c r="AT3"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M4" s="38"/>
       <c r="N4" s="38"/>
-    </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P4" s="74"/>
+      <c r="Q4" s="68"/>
+      <c r="AT4"/>
+      <c r="AV4" s="68"/>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M5" s="38"/>
       <c r="N5" s="38"/>
-    </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P5" s="74"/>
+      <c r="Q5" s="68"/>
+      <c r="AT5"/>
+      <c r="AV5" s="68"/>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M6" s="38"/>
       <c r="N6" s="38"/>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P6" s="74"/>
+      <c r="Q6" s="68"/>
+      <c r="AT6"/>
+      <c r="AV6" s="68"/>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M7" s="38"/>
       <c r="N7" s="38"/>
-    </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P7" s="74"/>
+      <c r="Q7" s="68"/>
+      <c r="AT7"/>
+      <c r="AV7" s="68"/>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M8" s="38"/>
       <c r="N8" s="38"/>
-    </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P8" s="74"/>
+      <c r="Q8" s="68"/>
+      <c r="AT8"/>
+      <c r="AV8" s="68"/>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M9" s="38"/>
       <c r="N9" s="38"/>
-    </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P9" s="74"/>
+      <c r="Q9" s="68"/>
+      <c r="AT9"/>
+      <c r="AV9" s="68"/>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M10" s="38"/>
       <c r="N10" s="38"/>
-    </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P10" s="74"/>
+      <c r="Q10" s="68"/>
+      <c r="AT10"/>
+      <c r="AV10" s="68"/>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M11" s="38"/>
       <c r="N11" s="38"/>
-    </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P11" s="74"/>
+      <c r="Q11" s="68"/>
+      <c r="AT11"/>
+      <c r="AV11" s="68"/>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M12" s="38"/>
       <c r="N12" s="38"/>
-    </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P12" s="74"/>
+      <c r="Q12" s="68"/>
+      <c r="AT12"/>
+      <c r="AV12" s="68"/>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M13" s="38"/>
       <c r="N13" s="38"/>
-    </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P13" s="74"/>
+      <c r="Q13" s="68"/>
+      <c r="AT13"/>
+      <c r="AV13" s="68"/>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M14" s="38"/>
       <c r="N14" s="38"/>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P14" s="74"/>
+      <c r="Q14" s="68"/>
+      <c r="AT14"/>
+      <c r="AV14" s="68"/>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M15" s="38"/>
       <c r="N15" s="38"/>
-    </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="P15" s="74"/>
+      <c r="Q15" s="68"/>
+      <c r="AT15"/>
+      <c r="AV15" s="68"/>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
-    </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P16" s="74"/>
+      <c r="Q16" s="68"/>
+      <c r="AT16"/>
+      <c r="AV16" s="68"/>
+    </row>
+    <row r="17" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M17" s="38"/>
       <c r="N17" s="38"/>
-    </row>
-    <row r="18" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P17" s="74"/>
+      <c r="Q17" s="68"/>
+      <c r="AT17"/>
+      <c r="AV17" s="68"/>
+    </row>
+    <row r="18" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M18" s="38"/>
       <c r="N18" s="38"/>
-    </row>
-    <row r="19" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P18" s="74"/>
+      <c r="Q18" s="68"/>
+      <c r="AT18"/>
+      <c r="AV18" s="68"/>
+    </row>
+    <row r="19" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M19" s="38"/>
       <c r="N19" s="38"/>
-    </row>
-    <row r="20" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P19" s="74"/>
+      <c r="Q19" s="68"/>
+      <c r="AT19"/>
+      <c r="AV19" s="68"/>
+    </row>
+    <row r="20" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
-    </row>
-    <row r="21" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P20" s="74"/>
+      <c r="Q20" s="68"/>
+      <c r="AT20"/>
+      <c r="AV20" s="68"/>
+    </row>
+    <row r="21" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M21" s="38"/>
       <c r="N21" s="38"/>
-    </row>
-    <row r="22" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P21" s="74"/>
+      <c r="Q21" s="68"/>
+      <c r="AT21"/>
+      <c r="AV21" s="68"/>
+    </row>
+    <row r="22" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M22" s="38"/>
       <c r="N22" s="38"/>
-    </row>
-    <row r="23" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P22" s="74"/>
+      <c r="Q22" s="68"/>
+      <c r="AT22"/>
+      <c r="AV22" s="68"/>
+    </row>
+    <row r="23" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M23" s="38"/>
       <c r="N23" s="38"/>
-    </row>
-    <row r="24" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P23" s="74"/>
+      <c r="Q23" s="68"/>
+      <c r="AT23"/>
+      <c r="AV23" s="68"/>
+    </row>
+    <row r="24" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M24" s="38"/>
       <c r="N24" s="38"/>
-    </row>
-    <row r="25" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P24" s="74"/>
+      <c r="Q24" s="68"/>
+      <c r="AT24"/>
+      <c r="AV24" s="68"/>
+    </row>
+    <row r="25" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M25" s="38"/>
       <c r="N25" s="38"/>
-    </row>
-    <row r="26" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P25" s="74"/>
+      <c r="Q25" s="68"/>
+      <c r="AT25"/>
+      <c r="AV25" s="68"/>
+    </row>
+    <row r="26" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M26" s="38"/>
       <c r="N26" s="38"/>
-    </row>
-    <row r="27" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P26" s="74"/>
+      <c r="Q26" s="68"/>
+      <c r="AT26"/>
+      <c r="AV26" s="68"/>
+    </row>
+    <row r="27" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M27" s="38"/>
       <c r="N27" s="38"/>
-    </row>
-    <row r="28" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P27" s="74"/>
+      <c r="Q27" s="68"/>
+      <c r="AT27"/>
+      <c r="AV27" s="68"/>
+    </row>
+    <row r="28" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M28" s="38"/>
       <c r="N28" s="38"/>
-    </row>
-    <row r="29" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P28" s="74"/>
+      <c r="Q28" s="68"/>
+      <c r="AT28"/>
+      <c r="AV28" s="68"/>
+    </row>
+    <row r="29" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M29" s="38"/>
       <c r="N29" s="38"/>
-    </row>
-    <row r="30" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P29" s="74"/>
+      <c r="Q29" s="68"/>
+      <c r="AT29"/>
+      <c r="AV29" s="68"/>
+    </row>
+    <row r="30" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M30" s="38"/>
       <c r="N30" s="38"/>
-    </row>
-    <row r="31" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P30" s="74"/>
+      <c r="Q30" s="68"/>
+      <c r="AT30"/>
+      <c r="AV30" s="68"/>
+    </row>
+    <row r="31" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M31" s="38"/>
       <c r="N31" s="38"/>
-    </row>
-    <row r="32" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P31" s="74"/>
+      <c r="Q31" s="68"/>
+      <c r="AT31"/>
+      <c r="AV31" s="68"/>
+    </row>
+    <row r="32" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M32" s="38"/>
       <c r="N32" s="38"/>
-    </row>
-    <row r="33" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P32" s="74"/>
+      <c r="Q32" s="68"/>
+      <c r="AT32"/>
+      <c r="AV32" s="68"/>
+    </row>
+    <row r="33" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M33" s="38"/>
       <c r="N33" s="38"/>
-    </row>
-    <row r="34" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P33" s="74"/>
+      <c r="Q33" s="68"/>
+      <c r="AT33"/>
+      <c r="AV33" s="68"/>
+    </row>
+    <row r="34" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M34" s="38"/>
       <c r="N34" s="38"/>
-    </row>
-    <row r="35" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P34" s="74"/>
+      <c r="Q34" s="68"/>
+      <c r="AT34"/>
+      <c r="AV34" s="68"/>
+    </row>
+    <row r="35" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M35" s="38"/>
       <c r="N35" s="38"/>
-    </row>
-    <row r="36" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P35" s="74"/>
+      <c r="Q35" s="68"/>
+      <c r="AT35"/>
+      <c r="AV35" s="68"/>
+    </row>
+    <row r="36" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M36" s="38"/>
       <c r="N36" s="38"/>
-    </row>
-    <row r="37" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P36" s="74"/>
+      <c r="Q36" s="68"/>
+      <c r="AT36"/>
+      <c r="AV36" s="68"/>
+    </row>
+    <row r="37" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M37" s="38"/>
       <c r="N37" s="38"/>
-    </row>
-    <row r="38" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P37" s="74"/>
+      <c r="Q37" s="68"/>
+      <c r="AT37"/>
+      <c r="AV37" s="68"/>
+    </row>
+    <row r="38" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M38" s="38"/>
       <c r="N38" s="38"/>
-    </row>
-    <row r="39" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P38" s="74"/>
+      <c r="Q38" s="68"/>
+      <c r="AT38"/>
+      <c r="AV38" s="68"/>
+    </row>
+    <row r="39" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M39" s="38"/>
       <c r="N39" s="38"/>
-    </row>
-    <row r="40" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P39" s="74"/>
+      <c r="Q39" s="68"/>
+      <c r="AT39"/>
+      <c r="AV39" s="68"/>
+    </row>
+    <row r="40" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M40" s="38"/>
       <c r="N40" s="38"/>
-    </row>
-    <row r="41" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P40" s="74"/>
+      <c r="Q40" s="68"/>
+      <c r="AT40"/>
+      <c r="AV40" s="68"/>
+    </row>
+    <row r="41" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M41" s="38"/>
       <c r="N41" s="38"/>
-    </row>
-    <row r="42" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P41" s="74"/>
+      <c r="Q41" s="68"/>
+      <c r="AT41"/>
+      <c r="AV41" s="68"/>
+    </row>
+    <row r="42" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M42" s="38"/>
       <c r="N42" s="38"/>
-    </row>
-    <row r="43" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P42" s="74"/>
+      <c r="Q42" s="68"/>
+      <c r="AT42"/>
+      <c r="AV42" s="68"/>
+    </row>
+    <row r="43" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M43" s="38"/>
       <c r="N43" s="38"/>
-    </row>
-    <row r="44" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P43" s="74"/>
+      <c r="Q43" s="68"/>
+      <c r="AT43"/>
+      <c r="AV43" s="68"/>
+    </row>
+    <row r="44" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M44" s="38"/>
       <c r="N44" s="38"/>
-    </row>
-    <row r="45" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P44" s="74"/>
+      <c r="Q44" s="68"/>
+      <c r="AT44"/>
+      <c r="AV44" s="68"/>
+    </row>
+    <row r="45" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M45" s="38"/>
       <c r="N45" s="38"/>
-    </row>
-    <row r="46" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P45" s="74"/>
+      <c r="Q45" s="68"/>
+      <c r="AT45"/>
+      <c r="AV45" s="68"/>
+    </row>
+    <row r="46" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M46" s="38"/>
       <c r="N46" s="38"/>
-    </row>
-    <row r="47" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P46" s="74"/>
+      <c r="Q46" s="68"/>
+      <c r="AT46"/>
+      <c r="AV46" s="68"/>
+    </row>
+    <row r="47" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M47" s="38"/>
       <c r="N47" s="38"/>
-    </row>
-    <row r="48" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P47" s="74"/>
+      <c r="Q47" s="68"/>
+      <c r="AT47"/>
+      <c r="AV47" s="68"/>
+    </row>
+    <row r="48" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M48" s="38"/>
       <c r="N48" s="38"/>
-    </row>
-    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P48" s="74"/>
+      <c r="Q48" s="68"/>
+      <c r="AT48"/>
+      <c r="AV48" s="68"/>
+    </row>
+    <row r="49" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M49" s="38"/>
       <c r="N49" s="38"/>
-    </row>
-    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P49" s="74"/>
+      <c r="Q49" s="68"/>
+      <c r="AT49"/>
+      <c r="AV49" s="68"/>
+    </row>
+    <row r="50" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M50" s="38"/>
       <c r="N50" s="38"/>
-    </row>
-    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P50" s="74"/>
+      <c r="Q50" s="68"/>
+      <c r="AT50"/>
+      <c r="AV50" s="68"/>
+    </row>
+    <row r="51" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M51" s="38"/>
       <c r="N51" s="38"/>
-    </row>
-    <row r="52" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P51" s="74"/>
+      <c r="Q51" s="68"/>
+      <c r="AT51"/>
+      <c r="AV51" s="68"/>
+    </row>
+    <row r="52" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M52" s="38"/>
       <c r="N52" s="38"/>
-    </row>
-    <row r="53" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P52" s="74"/>
+      <c r="Q52" s="68"/>
+      <c r="AT52"/>
+      <c r="AV52" s="68"/>
+    </row>
+    <row r="53" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M53" s="38"/>
       <c r="N53" s="38"/>
-    </row>
-    <row r="54" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P53" s="74"/>
+      <c r="Q53" s="68"/>
+      <c r="AT53"/>
+      <c r="AV53" s="68"/>
+    </row>
+    <row r="54" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M54" s="38"/>
       <c r="N54" s="38"/>
-    </row>
-    <row r="55" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P54" s="74"/>
+      <c r="Q54" s="68"/>
+      <c r="AT54"/>
+      <c r="AV54" s="68"/>
+    </row>
+    <row r="55" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M55" s="38"/>
       <c r="N55" s="38"/>
-    </row>
-    <row r="56" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P55" s="74"/>
+      <c r="Q55" s="68"/>
+      <c r="AT55"/>
+      <c r="AV55" s="68"/>
+    </row>
+    <row r="56" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M56" s="38"/>
       <c r="N56" s="38"/>
-    </row>
-    <row r="57" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P56" s="74"/>
+      <c r="Q56" s="68"/>
+      <c r="AT56"/>
+      <c r="AV56" s="68"/>
+    </row>
+    <row r="57" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M57" s="38"/>
       <c r="N57" s="38"/>
-    </row>
-    <row r="58" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P57" s="74"/>
+      <c r="Q57" s="68"/>
+      <c r="AT57"/>
+      <c r="AV57" s="68"/>
+    </row>
+    <row r="58" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M58" s="38"/>
       <c r="N58" s="38"/>
-    </row>
-    <row r="59" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P58" s="74"/>
+      <c r="Q58" s="68"/>
+      <c r="AT58"/>
+      <c r="AV58" s="68"/>
+    </row>
+    <row r="59" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M59" s="38"/>
       <c r="N59" s="38"/>
-    </row>
-    <row r="60" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P59" s="74"/>
+      <c r="Q59" s="68"/>
+      <c r="AT59"/>
+      <c r="AV59" s="68"/>
+    </row>
+    <row r="60" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M60" s="38"/>
       <c r="N60" s="38"/>
-    </row>
-    <row r="61" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P60" s="74"/>
+      <c r="Q60" s="68"/>
+      <c r="AT60"/>
+      <c r="AV60" s="68"/>
+    </row>
+    <row r="61" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M61" s="38"/>
       <c r="N61" s="38"/>
-    </row>
-    <row r="62" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P61" s="74"/>
+      <c r="Q61" s="68"/>
+      <c r="AT61"/>
+      <c r="AV61" s="68"/>
+    </row>
+    <row r="62" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M62" s="38"/>
       <c r="N62" s="38"/>
-    </row>
-    <row r="63" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P62" s="74"/>
+      <c r="Q62" s="68"/>
+      <c r="AT62"/>
+      <c r="AV62" s="68"/>
+    </row>
+    <row r="63" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M63" s="38"/>
       <c r="N63" s="38"/>
-    </row>
-    <row r="64" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P63" s="74"/>
+      <c r="Q63" s="68"/>
+      <c r="AT63"/>
+      <c r="AV63" s="68"/>
+    </row>
+    <row r="64" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M64" s="38"/>
       <c r="N64" s="38"/>
-    </row>
-    <row r="65" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P64" s="74"/>
+      <c r="Q64" s="68"/>
+      <c r="AT64"/>
+      <c r="AV64" s="68"/>
+    </row>
+    <row r="65" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M65" s="38"/>
       <c r="N65" s="38"/>
-    </row>
-    <row r="66" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P65" s="74"/>
+      <c r="Q65" s="68"/>
+      <c r="AT65"/>
+      <c r="AV65" s="68"/>
+    </row>
+    <row r="66" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M66" s="38"/>
       <c r="N66" s="38"/>
-    </row>
-    <row r="67" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P66" s="74"/>
+      <c r="Q66" s="68"/>
+      <c r="AT66"/>
+      <c r="AV66" s="68"/>
+    </row>
+    <row r="67" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M67" s="38"/>
       <c r="N67" s="38"/>
-    </row>
-    <row r="68" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P67" s="74"/>
+      <c r="Q67" s="68"/>
+      <c r="AT67"/>
+      <c r="AV67" s="68"/>
+    </row>
+    <row r="68" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M68" s="38"/>
       <c r="N68" s="38"/>
-    </row>
-    <row r="69" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P68" s="74"/>
+      <c r="Q68" s="68"/>
+      <c r="AT68"/>
+      <c r="AV68" s="68"/>
+    </row>
+    <row r="69" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M69" s="38"/>
       <c r="N69" s="38"/>
-    </row>
-    <row r="70" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P69" s="74"/>
+      <c r="Q69" s="68"/>
+      <c r="AT69"/>
+      <c r="AV69" s="68"/>
+    </row>
+    <row r="70" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M70" s="38"/>
       <c r="N70" s="38"/>
-    </row>
-    <row r="71" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P70" s="74"/>
+      <c r="Q70" s="68"/>
+      <c r="AT70"/>
+      <c r="AV70" s="68"/>
+    </row>
+    <row r="71" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M71" s="38"/>
       <c r="N71" s="38"/>
-    </row>
-    <row r="72" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P71" s="74"/>
+      <c r="Q71" s="68"/>
+      <c r="AT71"/>
+      <c r="AV71" s="68"/>
+    </row>
+    <row r="72" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M72" s="38"/>
       <c r="N72" s="38"/>
-    </row>
-    <row r="73" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P72" s="74"/>
+      <c r="Q72" s="68"/>
+      <c r="AT72"/>
+      <c r="AV72" s="68"/>
+    </row>
+    <row r="73" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M73" s="38"/>
       <c r="N73" s="38"/>
-    </row>
-    <row r="74" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P73" s="74"/>
+      <c r="Q73" s="68"/>
+      <c r="AT73"/>
+      <c r="AV73" s="68"/>
+    </row>
+    <row r="74" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M74" s="38"/>
       <c r="N74" s="38"/>
-    </row>
-    <row r="75" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P74" s="74"/>
+      <c r="Q74" s="68"/>
+      <c r="AT74"/>
+      <c r="AV74" s="68"/>
+    </row>
+    <row r="75" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M75" s="38"/>
       <c r="N75" s="38"/>
-    </row>
-    <row r="76" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P75" s="74"/>
+      <c r="Q75" s="68"/>
+      <c r="AT75"/>
+      <c r="AV75" s="68"/>
+    </row>
+    <row r="76" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M76" s="38"/>
       <c r="N76" s="38"/>
-    </row>
-    <row r="77" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P76" s="74"/>
+      <c r="Q76" s="68"/>
+      <c r="AT76"/>
+      <c r="AV76" s="68"/>
+    </row>
+    <row r="77" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M77" s="38"/>
       <c r="N77" s="38"/>
-    </row>
-    <row r="78" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P77" s="74"/>
+      <c r="Q77" s="68"/>
+      <c r="AT77"/>
+      <c r="AV77" s="68"/>
+    </row>
+    <row r="78" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M78" s="38"/>
       <c r="N78" s="38"/>
-    </row>
-    <row r="79" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P78" s="74"/>
+      <c r="Q78" s="68"/>
+      <c r="AT78"/>
+      <c r="AV78" s="68"/>
+    </row>
+    <row r="79" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M79" s="38"/>
       <c r="N79" s="38"/>
-    </row>
-    <row r="80" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P79" s="74"/>
+      <c r="Q79" s="68"/>
+      <c r="AT79"/>
+      <c r="AV79" s="68"/>
+    </row>
+    <row r="80" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M80" s="38"/>
       <c r="N80" s="38"/>
-    </row>
-    <row r="81" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P80" s="74"/>
+      <c r="Q80" s="68"/>
+      <c r="AT80"/>
+      <c r="AV80" s="68"/>
+    </row>
+    <row r="81" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M81" s="38"/>
       <c r="N81" s="38"/>
-    </row>
-    <row r="82" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P81" s="74"/>
+      <c r="Q81" s="68"/>
+      <c r="AT81"/>
+      <c r="AV81" s="68"/>
+    </row>
+    <row r="82" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M82" s="38"/>
       <c r="N82" s="38"/>
-    </row>
-    <row r="83" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P82" s="74"/>
+      <c r="Q82" s="68"/>
+      <c r="AT82"/>
+      <c r="AV82" s="68"/>
+    </row>
+    <row r="83" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M83" s="38"/>
       <c r="N83" s="38"/>
-    </row>
-    <row r="84" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P83" s="74"/>
+      <c r="Q83" s="68"/>
+      <c r="AT83"/>
+      <c r="AV83" s="68"/>
+    </row>
+    <row r="84" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M84" s="38"/>
       <c r="N84" s="38"/>
-    </row>
-    <row r="85" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P84" s="74"/>
+      <c r="Q84" s="68"/>
+      <c r="AT84"/>
+      <c r="AV84" s="68"/>
+    </row>
+    <row r="85" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M85" s="38"/>
       <c r="N85" s="38"/>
-    </row>
-    <row r="86" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P85" s="74"/>
+      <c r="Q85" s="68"/>
+      <c r="AT85"/>
+      <c r="AV85" s="68"/>
+    </row>
+    <row r="86" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M86" s="38"/>
       <c r="N86" s="38"/>
-    </row>
-    <row r="87" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P86" s="74"/>
+      <c r="Q86" s="68"/>
+      <c r="AT86"/>
+      <c r="AV86" s="68"/>
+    </row>
+    <row r="87" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M87" s="38"/>
       <c r="N87" s="38"/>
-    </row>
-    <row r="88" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P87" s="74"/>
+      <c r="Q87" s="68"/>
+      <c r="AT87"/>
+      <c r="AV87" s="68"/>
+    </row>
+    <row r="88" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M88" s="38"/>
       <c r="N88" s="38"/>
-    </row>
-    <row r="89" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P88" s="74"/>
+      <c r="Q88" s="68"/>
+      <c r="AT88"/>
+      <c r="AV88" s="68"/>
+    </row>
+    <row r="89" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M89" s="38"/>
       <c r="N89" s="38"/>
-    </row>
-    <row r="90" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P89" s="74"/>
+      <c r="Q89" s="68"/>
+      <c r="AT89"/>
+      <c r="AV89" s="68"/>
+    </row>
+    <row r="90" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M90" s="38"/>
       <c r="N90" s="38"/>
-    </row>
-    <row r="91" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P90" s="74"/>
+      <c r="Q90" s="68"/>
+      <c r="AT90"/>
+      <c r="AV90" s="68"/>
+    </row>
+    <row r="91" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M91" s="38"/>
       <c r="N91" s="38"/>
-    </row>
-    <row r="92" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P91" s="74"/>
+      <c r="Q91" s="68"/>
+      <c r="AT91"/>
+      <c r="AV91" s="68"/>
+    </row>
+    <row r="92" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M92" s="38"/>
       <c r="N92" s="38"/>
-    </row>
-    <row r="93" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P92" s="74"/>
+      <c r="Q92" s="68"/>
+      <c r="AT92"/>
+      <c r="AV92" s="68"/>
+    </row>
+    <row r="93" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M93" s="38"/>
       <c r="N93" s="38"/>
-    </row>
-    <row r="94" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P93" s="74"/>
+      <c r="Q93" s="68"/>
+      <c r="AT93"/>
+      <c r="AV93" s="68"/>
+    </row>
+    <row r="94" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M94" s="38"/>
       <c r="N94" s="38"/>
-    </row>
-    <row r="95" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P94" s="74"/>
+      <c r="Q94" s="68"/>
+      <c r="AT94"/>
+      <c r="AV94" s="68"/>
+    </row>
+    <row r="95" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M95" s="38"/>
       <c r="N95" s="38"/>
-    </row>
-    <row r="96" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P95" s="74"/>
+      <c r="Q95" s="68"/>
+      <c r="AT95"/>
+      <c r="AV95" s="68"/>
+    </row>
+    <row r="96" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M96" s="38"/>
       <c r="N96" s="38"/>
-    </row>
-    <row r="97" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P96" s="74"/>
+      <c r="Q96" s="68"/>
+      <c r="AT96"/>
+      <c r="AV96" s="68"/>
+    </row>
+    <row r="97" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M97" s="38"/>
       <c r="N97" s="38"/>
-    </row>
-    <row r="98" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P97" s="74"/>
+      <c r="Q97" s="68"/>
+      <c r="AT97"/>
+      <c r="AV97" s="68"/>
+    </row>
+    <row r="98" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M98" s="38"/>
       <c r="N98" s="38"/>
-    </row>
-    <row r="99" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P98" s="74"/>
+      <c r="Q98" s="68"/>
+      <c r="AT98"/>
+      <c r="AV98" s="68"/>
+    </row>
+    <row r="99" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M99" s="38"/>
       <c r="N99" s="38"/>
-    </row>
-    <row r="100" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="P99" s="74"/>
+      <c r="Q99" s="68"/>
+      <c r="AT99"/>
+      <c r="AV99" s="68"/>
+    </row>
+    <row r="100" spans="13:48" x14ac:dyDescent="0.3">
       <c r="M100" s="38"/>
       <c r="N100" s="38"/>
+      <c r="P100" s="74"/>
+      <c r="Q100" s="68"/>
+      <c r="AT100"/>
+      <c r="AV100" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="P1:AT1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2744,7 +3203,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="fertilizer" prompt="select type" xr:uid="{B70B515A-9E4D-43A4-A403-3B52F4B6E7A5}">
           <x14:formula1>
             <xm:f>options!$C$2:$C$9</xm:f>
@@ -2756,6 +3215,12 @@
             <xm:f>options!$E$2:$E$3</xm:f>
           </x14:formula1>
           <xm:sqref>N3:N100</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="irrigation location" prompt="Indicate if irrigation applied aboveground (either above or below plant canopy) or belowground (i.e. drip). " xr:uid="{D1AF471D-DDE0-4230-AA87-8B03F8E0C30A}">
+          <x14:formula1>
+            <xm:f>options!$K$2:$K$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>P3:P100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2797,85 +3262,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.3">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="52" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="51" t="s">
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56"/>
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="55" t="s">
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="55"/>
+      <c r="AR1" s="55"/>
+      <c r="AS1" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="AT1" s="55"/>
-      <c r="AU1" s="55"/>
-      <c r="AV1" s="55"/>
-      <c r="AW1" s="55"/>
-      <c r="AX1" s="55"/>
-      <c r="AY1" s="55"/>
-      <c r="AZ1" s="55"/>
-      <c r="BA1" s="55"/>
-      <c r="BB1" s="55"/>
-      <c r="BC1" s="55"/>
-      <c r="BD1" s="55"/>
-      <c r="BE1" s="57"/>
-      <c r="BF1" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG1" s="58"/>
-      <c r="BH1" s="58"/>
-      <c r="BI1" s="58"/>
-      <c r="BJ1" s="58"/>
-      <c r="BK1" s="58"/>
-      <c r="BL1" s="58"/>
-      <c r="BM1" s="58"/>
-      <c r="BN1" s="58"/>
-      <c r="BO1" s="58"/>
-      <c r="BP1" s="58"/>
-      <c r="BQ1" s="58"/>
-      <c r="BR1" s="59"/>
+      <c r="AT1" s="59"/>
+      <c r="AU1" s="59"/>
+      <c r="AV1" s="59"/>
+      <c r="AW1" s="59"/>
+      <c r="AX1" s="59"/>
+      <c r="AY1" s="59"/>
+      <c r="AZ1" s="59"/>
+      <c r="BA1" s="59"/>
+      <c r="BB1" s="59"/>
+      <c r="BC1" s="59"/>
+      <c r="BD1" s="59"/>
+      <c r="BE1" s="61"/>
+      <c r="BF1" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="62"/>
+      <c r="BJ1" s="62"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="62"/>
+      <c r="BM1" s="62"/>
+      <c r="BN1" s="62"/>
+      <c r="BO1" s="62"/>
+      <c r="BP1" s="62"/>
+      <c r="BQ1" s="62"/>
+      <c r="BR1" s="63"/>
     </row>
     <row r="2" spans="1:71" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
@@ -2888,7 +3353,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>11</v>
@@ -2900,40 +3365,40 @@
         <v>13</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I2" s="27" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="K2" s="27" t="s">
         <v>126</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>127</v>
       </c>
       <c r="L2" s="27" t="s">
         <v>43</v>
       </c>
       <c r="M2" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N2" s="27" t="s">
         <v>44</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>15</v>
       </c>
       <c r="Q2" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R2" s="29" t="s">
         <v>16</v>
       </c>
       <c r="S2" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T2" s="30" t="s">
         <v>18</v>
@@ -2954,25 +3419,25 @@
         <v>45</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA2" s="30" t="s">
         <v>46</v>
       </c>
       <c r="AB2" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>23</v>
       </c>
       <c r="AD2" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AE2" s="31" t="s">
         <v>24</v>
       </c>
       <c r="AF2" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG2" s="32" t="s">
         <v>25</v>
@@ -2993,25 +3458,25 @@
         <v>47</v>
       </c>
       <c r="AM2" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN2" s="32" t="s">
         <v>48</v>
       </c>
       <c r="AO2" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AP2" s="32" t="s">
         <v>30</v>
       </c>
       <c r="AQ2" s="34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AR2" s="33" t="s">
         <v>31</v>
       </c>
       <c r="AS2" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AT2" s="36" t="s">
         <v>32</v>
@@ -3032,64 +3497,64 @@
         <v>49</v>
       </c>
       <c r="AZ2" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BA2" s="36" t="s">
         <v>50</v>
       </c>
       <c r="BB2" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BC2" s="36" t="s">
         <v>37</v>
       </c>
       <c r="BD2" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BE2" s="36" t="s">
         <v>38</v>
       </c>
       <c r="BF2" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BG2" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="BH2" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="BH2" s="46" t="s">
+      <c r="BI2" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="BI2" s="46" t="s">
+      <c r="BJ2" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="BJ2" s="46" t="s">
+      <c r="BK2" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="BK2" s="46" t="s">
+      <c r="BL2" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="BL2" s="46" t="s">
+      <c r="BM2" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="BM2" s="47" t="s">
+      <c r="BN2" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="BN2" s="46" t="s">
+      <c r="BO2" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="BO2" s="47" t="s">
+      <c r="BP2" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="BP2" s="46" t="s">
+      <c r="BQ2" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="BQ2" s="47" t="s">
+      <c r="BR2" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="BR2" s="46" t="s">
+      <c r="BS2" s="48" t="s">
         <v>162</v>
-      </c>
-      <c r="BS2" s="48" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.3">
@@ -6477,16 +6942,16 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C1"/>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="61"/>
-      <c r="I1" s="62" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="67"/>
+      <c r="I1" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="63"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
@@ -7061,23 +7526,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="51" t="s">
         <v>165</v>
-      </c>
-      <c r="E1" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="64" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -7189,7 +7654,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA73EF4-F459-4FB8-999B-97CF29F368C2}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.21875" customWidth="1"/>
@@ -7197,9 +7662,10 @@
     <col min="5" max="5" width="20.44140625" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="11" max="11" width="18.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>72</v>
       </c>
@@ -7210,13 +7676,16 @@
         <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+      <c r="K1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -7227,13 +7696,16 @@
         <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="K2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -7244,21 +7716,27 @@
         <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+      <c r="K3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -7266,37 +7744,38 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="5">
+  <tableParts count="6">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
